--- a/SWOT/SWOT-modelo.xlsx
+++ b/SWOT/SWOT-modelo.xlsx
@@ -19,12 +19,12 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$M$56</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$M$55</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$M$57</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$M$56</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$49</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Plano de ação'!$B$1:$I$29</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Priorização!$B$1:$I$70</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">SWOT!$B$1:$M$47</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">SWOT!$B$1:$M$48</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'SWOT cruzada'!$B$1:$I$27</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="298">
   <si>
     <t xml:space="preserve">SWOT — Como usar esta planilha</t>
   </si>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">SWOT</t>
   </si>
   <si>
-    <t xml:space="preserve">Modelo principal. Cabeçalho da análise, quatro quadrantes com notas e resumo automático.</t>
+    <t xml:space="preserve">Modelo principal. Cabeçalho da análise, quatro quadrantes com notas e resumo automático, com a média por quadrante.</t>
   </si>
   <si>
     <t xml:space="preserve">Priorização</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Exemplo 2 - Compras</t>
   </si>
   <si>
-    <t xml:space="preserve">Análise preenchida com postura de sobrevivência: reduzir o custo de aquisição.</t>
+    <t xml:space="preserve">Análise preenchida com postura de manutenção: reduzir o custo de aquisição.</t>
   </si>
   <si>
     <t xml:space="preserve">Regras e premissas do modelo</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">Postura estratégica</t>
   </si>
   <si>
-    <t xml:space="preserve">A postura compara a soma dos pontos dos quadrantes: forças com fraquezas e oportunidades com ameaças. É uma leitura de apoio, que depende das notas dadas pelo grupo.</t>
+    <t xml:space="preserve">A postura compara a média dos pontos por fator de cada quadrante: forças com fraquezas e oportunidades com ameaças. A média, e não a soma, para que um quadrante não pese mais só por ter mais fatores. É uma leitura de apoio, que depende das notas dadas pelo grupo.</t>
   </si>
   <si>
     <t xml:space="preserve">Empates</t>
@@ -569,13 +569,16 @@
     <t xml:space="preserve">Fatores listados</t>
   </si>
   <si>
+    <t xml:space="preserve">Média por fator</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aviso</t>
   </si>
   <si>
-    <t xml:space="preserve">Balanço interno (forças menos fraquezas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balanço externo (oportunidades menos ameaças)</t>
+    <t xml:space="preserve">Balanço interno (média das forças menos a das fraquezas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanço externo (média das oportunidades menos a das ameaças)</t>
   </si>
   <si>
     <t xml:space="preserve">Postura estratégica sugerida</t>
@@ -905,10 +908,10 @@
     <t xml:space="preserve">Estratégias da SWOT cruzada</t>
   </si>
   <si>
-    <t xml:space="preserve">S3 × O4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lançar o pedido por mensagem, com programa de fidelidade para os clientes do bairro.</t>
+    <t xml:space="preserve">S2 × O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lançar o pedido por mensagem, com a entrega própria no prazo como argumento.</t>
   </si>
   <si>
     <t xml:space="preserve">S1 × O1</t>
@@ -929,19 +932,19 @@
     <t xml:space="preserve">Avaliar a compra do segundo forno antes da entrega dos condomínios.</t>
   </si>
   <si>
-    <t xml:space="preserve">S2 × T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Divulgar a entrega no prazo como diferencial diante da rede concorrente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3 × T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implantar ficha técnica e custo por pizza, para reagir às altas de preço.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Área de Suprimentos de uma indústria</t>
+    <t xml:space="preserve">S2 × T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divulgar a entrega própria no prazo para levar os clientes do aplicativo ao canal próprio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W2 × T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negociar a taxa com o aplicativo e definir preços por canal, para que o aumento não consuma a margem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribuidora de materiais elétricos · Compras</t>
   </si>
   <si>
     <t xml:space="preserve">Gerente de Suprimentos</t>
@@ -971,7 +974,7 @@
     <t xml:space="preserve">Base de fornecedores homologados para todos os itens críticos</t>
   </si>
   <si>
-    <t xml:space="preserve">Processo manual, em planilhas e e-mails</t>
+    <t xml:space="preserve">Cotações e aprovações por e-mail, fora do sistema de compras</t>
   </si>
   <si>
     <t xml:space="preserve">Contratos de longo prazo para os principais insumos</t>
@@ -1035,15 +1038,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0&quot; fatores&quot;"/>
     <numFmt numFmtId="167" formatCode="0&quot; pontos&quot;"/>
-    <numFmt numFmtId="168" formatCode="General"/>
-    <numFmt numFmtId="169" formatCode="\+0;\-0;0"/>
-    <numFmt numFmtId="170" formatCode="0&quot; de 10&quot;"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="General"/>
+    <numFmt numFmtId="170" formatCode="\+0.0;\-0.0;0.0"/>
+    <numFmt numFmtId="171" formatCode="0&quot; de 10&quot;"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -1308,7 +1312,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1477,7 +1481,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1485,11 +1497,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1501,11 +1509,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1521,7 +1529,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1959,11 +1967,11 @@
         </c:ser>
         <c:gapWidth val="120"/>
         <c:overlap val="0"/>
-        <c:axId val="28722330"/>
-        <c:axId val="29384934"/>
+        <c:axId val="44875571"/>
+        <c:axId val="72586805"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="28722330"/>
+        <c:axId val="44875571"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1995,7 +2003,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29384934"/>
+        <c:crossAx val="72586805"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2003,7 +2011,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29384934"/>
+        <c:axId val="72586805"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2043,7 +2051,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28722330"/>
+        <c:crossAx val="44875571"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2643,7 +2651,7 @@
     <tabColor rgb="FF1E7B73"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:M47"/>
+  <dimension ref="B1:M48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3520,50 +3528,59 @@
       <c r="L42" s="41"/>
       <c r="M42" s="41"/>
     </row>
-    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="39" t="s">
         <v>143</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
       <c r="E43" s="42" t="str">
-        <f aca="false">IF(E41=0,"Liste os fatores",IF(E41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(G16:G23)&lt;E41,"Há fator sem nota","OK")))</f>
-        <v>Liste os fatores</v>
+        <f aca="false">IF(COUNT(G16:G23)=0,"",AVERAGE(G16:G23))</f>
+        <v/>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
       <c r="H43" s="42" t="str">
+        <f aca="false">IF(COUNT(M16:M23)=0,"",AVERAGE(M16:M23))</f>
+        <v/>
+      </c>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42" t="str">
+        <f aca="false">IF(COUNT(G30:G37)=0,"",AVERAGE(G30:G37))</f>
+        <v/>
+      </c>
+      <c r="K43" s="42" t="str">
+        <f aca="false">IF(COUNT(M30:M37)=0,"",AVERAGE(M30:M37))</f>
+        <v/>
+      </c>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="43" t="str">
+        <f aca="false">IF(E41=0,"Liste os fatores",IF(E41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(G16:G23)&lt;E41,"Há fator sem nota","OK")))</f>
+        <v>Liste os fatores</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43" t="str">
         <f aca="false">IF(H41=0,"Liste os fatores",IF(H41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(M16:M23)&lt;H41,"Há fator sem nota","OK")))</f>
         <v>Liste os fatores</v>
       </c>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42" t="str">
+      <c r="I44" s="43"/>
+      <c r="J44" s="43" t="str">
         <f aca="false">IF(J41=0,"Liste os fatores",IF(J41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(G30:G37)&lt;J41,"Há fator sem nota","OK")))</f>
         <v>Liste os fatores</v>
       </c>
-      <c r="K43" s="42" t="str">
+      <c r="K44" s="43" t="str">
         <f aca="false">IF(K41=0,"Liste os fatores",IF(K41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(M30:M37)&lt;K41,"Há fator sem nota","OK")))</f>
         <v>Liste os fatores</v>
       </c>
-      <c r="L43" s="42"/>
-      <c r="M43" s="42"/>
-    </row>
-    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="43" t="n">
-        <f aca="false">E42-H42</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
       <c r="L44" s="43"/>
       <c r="M44" s="43"/>
     </row>
@@ -3576,17 +3593,17 @@
       <c r="E45" s="39"/>
       <c r="F45" s="39"/>
       <c r="G45" s="39"/>
-      <c r="H45" s="43" t="n">
-        <f aca="false">J42-K42</f>
-        <v>0</v>
-      </c>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-    </row>
-    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H45" s="44" t="str">
+        <f aca="false">IF(OR(E43="",H43=""),"",E43-H43)</f>
+        <v/>
+      </c>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
+      <c r="M45" s="44"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="39" t="s">
         <v>146</v>
       </c>
@@ -3596,8 +3613,8 @@
       <c r="F46" s="39"/>
       <c r="G46" s="39"/>
       <c r="H46" s="44" t="str">
-        <f aca="false">IF(OR(COUNT(G16:G23)=0,COUNT(M16:M23)=0,COUNT(G30:G37)=0,COUNT(M30:M37)=0),"Dê notas aos quatro quadrantes para ver a postura",IF(E42&gt;=H42,IF(J42&gt;=K42,"Desenvolvimento: usar as forças para aproveitar as oportunidades","Manutenção: usar as forças para enfrentar as ameaças"),IF(J42&gt;=K42,"Crescimento: corrigir as fraquezas para aproveitar as oportunidades","Sobrevivência: reduzir as fraquezas e proteger-se das ameaças")))</f>
-        <v>Dê notas aos quatro quadrantes para ver a postura</v>
+        <f aca="false">IF(OR(J43="",K43=""),"",J43-K43)</f>
+        <v/>
       </c>
       <c r="I46" s="44"/>
       <c r="J46" s="44"/>
@@ -3605,7 +3622,7 @@
       <c r="L46" s="44"/>
       <c r="M46" s="44"/>
     </row>
-    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="39" t="s">
         <v>147</v>
       </c>
@@ -3614,9 +3631,9 @@
       <c r="E47" s="39"/>
       <c r="F47" s="39"/>
       <c r="G47" s="39"/>
-      <c r="H47" s="45" t="n">
-        <f aca="false">COUNTA(D4,J4,D5,J5,D6,J6,D7,D8,J8,D9)</f>
-        <v>0</v>
+      <c r="H47" s="45" t="str">
+        <f aca="false">IF(OR(COUNT(G16:G23)=0,COUNT(M16:M23)=0,COUNT(G30:G37)=0,COUNT(M30:M37)=0),"Dê notas aos quatro quadrantes para ver a postura",IF(E43&gt;=H43,IF(J43&gt;=K43,"Desenvolvimento: usar as forças para aproveitar as oportunidades","Manutenção: usar as forças para enfrentar as ameaças"),IF(J43&gt;=K43,"Crescimento: corrigir as fraquezas para aproveitar as oportunidades","Sobrevivência: reduzir as fraquezas e proteger-se das ameaças")))</f>
+        <v>Dê notas aos quatro quadrantes para ver a postura</v>
       </c>
       <c r="I47" s="45"/>
       <c r="J47" s="45"/>
@@ -3624,8 +3641,27 @@
       <c r="L47" s="45"/>
       <c r="M47" s="45"/>
     </row>
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="46" t="n">
+        <f aca="false">COUNTA(D4,J4,D5,J5,D6,J6,D7,D8,J8,D9)</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="46"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="46"/>
+      <c r="L48" s="46"/>
+      <c r="M48" s="46"/>
+    </row>
   </sheetData>
-  <mergeCells count="99">
+  <mergeCells count="103">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:C4"/>
@@ -3717,16 +3753,20 @@
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="K43:M43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="K44:M44"/>
     <mergeCell ref="B45:G45"/>
     <mergeCell ref="H45:M45"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="H46:M46"/>
     <mergeCell ref="B47:G47"/>
     <mergeCell ref="H47:M47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="H48:M48"/>
   </mergeCells>
-  <conditionalFormatting sqref="E43:M43">
+  <conditionalFormatting sqref="E44:M44">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -3785,7 +3825,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3797,7 +3837,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3809,7 +3849,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
@@ -3818,22 +3858,22 @@
       <c r="G4" s="38"/>
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
-      <c r="L4" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
+      <c r="L4" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D5" s="29" t="s">
         <v>137</v>
@@ -3851,39 +3891,39 @@
         <v>29</v>
       </c>
       <c r="I5" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="L5" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="L5" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="M5" s="47" t="s">
+      <c r="M5" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="N5" s="47" t="s">
+      <c r="N5" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="O5" s="47" t="s">
+      <c r="O5" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="P5" s="47" t="s">
+      <c r="P5" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="Q5" s="47" t="s">
+      <c r="Q5" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="R5" s="47" t="s">
-        <v>155</v>
+      <c r="R5" s="48" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="44" t="str">
+      <c r="C6" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B6,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D6" s="48" t="str">
+      <c r="D6" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B6,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -3891,11 +3931,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B6,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="49" t="str">
+      <c r="F6" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B6,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G6" s="49" t="str">
+      <c r="G6" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B6,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -3903,33 +3943,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B6,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I6" s="49" t="str">
+      <c r="I6" s="50" t="str">
         <f aca="false">IF(H6="","",IF(H6&gt;=15,"Alta",IF(H6&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L6" s="50" t="s">
+      <c r="L6" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="M6" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N6" s="51" t="str">
+      <c r="M6" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N6" s="52" t="str">
         <f aca="false">IF(SWOT!C16="","",SWOT!C16)</f>
         <v/>
       </c>
-      <c r="O6" s="50" t="str">
+      <c r="O6" s="51" t="str">
         <f aca="false">IF(SWOT!E16="","",SWOT!E16)</f>
         <v/>
       </c>
-      <c r="P6" s="50" t="str">
+      <c r="P6" s="51" t="str">
         <f aca="false">IF(SWOT!F16="","",SWOT!F16)</f>
         <v/>
       </c>
-      <c r="Q6" s="50" t="str">
+      <c r="Q6" s="51" t="str">
         <f aca="false">IF(SWOT!G16="","",SWOT!G16)</f>
         <v/>
       </c>
-      <c r="R6" s="50" t="str">
+      <c r="R6" s="51" t="str">
         <f aca="false">IF(Q6="","",RANK(Q6,$Q$6:$Q$37)+COUNTIF($Q$5:Q5,Q6))</f>
         <v/>
       </c>
@@ -3938,11 +3978,11 @@
       <c r="B7" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="44" t="str">
+      <c r="C7" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B7,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D7" s="48" t="str">
+      <c r="D7" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B7,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -3950,11 +3990,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B7,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F7" s="49" t="str">
+      <c r="F7" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B7,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G7" s="49" t="str">
+      <c r="G7" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B7,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -3962,33 +4002,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B7,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I7" s="49" t="str">
+      <c r="I7" s="50" t="str">
         <f aca="false">IF(H7="","",IF(H7&gt;=15,"Alta",IF(H7&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L7" s="50" t="s">
+      <c r="L7" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="M7" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N7" s="51" t="str">
+      <c r="M7" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N7" s="52" t="str">
         <f aca="false">IF(SWOT!C17="","",SWOT!C17)</f>
         <v/>
       </c>
-      <c r="O7" s="50" t="str">
+      <c r="O7" s="51" t="str">
         <f aca="false">IF(SWOT!E17="","",SWOT!E17)</f>
         <v/>
       </c>
-      <c r="P7" s="50" t="str">
+      <c r="P7" s="51" t="str">
         <f aca="false">IF(SWOT!F17="","",SWOT!F17)</f>
         <v/>
       </c>
-      <c r="Q7" s="50" t="str">
+      <c r="Q7" s="51" t="str">
         <f aca="false">IF(SWOT!G17="","",SWOT!G17)</f>
         <v/>
       </c>
-      <c r="R7" s="50" t="str">
+      <c r="R7" s="51" t="str">
         <f aca="false">IF(Q7="","",RANK(Q7,$Q$6:$Q$37)+COUNTIF($Q$5:Q6,Q7))</f>
         <v/>
       </c>
@@ -3997,11 +4037,11 @@
       <c r="B8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="44" t="str">
+      <c r="C8" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B8,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D8" s="48" t="str">
+      <c r="D8" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B8,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4009,11 +4049,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B8,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F8" s="49" t="str">
+      <c r="F8" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B8,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G8" s="49" t="str">
+      <c r="G8" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B8,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4021,33 +4061,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B8,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I8" s="49" t="str">
+      <c r="I8" s="50" t="str">
         <f aca="false">IF(H8="","",IF(H8&gt;=15,"Alta",IF(H8&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L8" s="50" t="s">
+      <c r="L8" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="M8" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N8" s="51" t="str">
+      <c r="M8" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N8" s="52" t="str">
         <f aca="false">IF(SWOT!C18="","",SWOT!C18)</f>
         <v/>
       </c>
-      <c r="O8" s="50" t="str">
+      <c r="O8" s="51" t="str">
         <f aca="false">IF(SWOT!E18="","",SWOT!E18)</f>
         <v/>
       </c>
-      <c r="P8" s="50" t="str">
+      <c r="P8" s="51" t="str">
         <f aca="false">IF(SWOT!F18="","",SWOT!F18)</f>
         <v/>
       </c>
-      <c r="Q8" s="50" t="str">
+      <c r="Q8" s="51" t="str">
         <f aca="false">IF(SWOT!G18="","",SWOT!G18)</f>
         <v/>
       </c>
-      <c r="R8" s="50" t="str">
+      <c r="R8" s="51" t="str">
         <f aca="false">IF(Q8="","",RANK(Q8,$Q$6:$Q$37)+COUNTIF($Q$5:Q7,Q8))</f>
         <v/>
       </c>
@@ -4056,11 +4096,11 @@
       <c r="B9" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="44" t="str">
+      <c r="C9" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B9,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="48" t="str">
+      <c r="D9" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B9,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4068,11 +4108,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B9,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F9" s="49" t="str">
+      <c r="F9" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B9,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G9" s="49" t="str">
+      <c r="G9" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B9,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4080,33 +4120,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B9,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I9" s="49" t="str">
+      <c r="I9" s="50" t="str">
         <f aca="false">IF(H9="","",IF(H9&gt;=15,"Alta",IF(H9&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L9" s="50" t="s">
+      <c r="L9" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="M9" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N9" s="51" t="str">
+      <c r="M9" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N9" s="52" t="str">
         <f aca="false">IF(SWOT!C19="","",SWOT!C19)</f>
         <v/>
       </c>
-      <c r="O9" s="50" t="str">
+      <c r="O9" s="51" t="str">
         <f aca="false">IF(SWOT!E19="","",SWOT!E19)</f>
         <v/>
       </c>
-      <c r="P9" s="50" t="str">
+      <c r="P9" s="51" t="str">
         <f aca="false">IF(SWOT!F19="","",SWOT!F19)</f>
         <v/>
       </c>
-      <c r="Q9" s="50" t="str">
+      <c r="Q9" s="51" t="str">
         <f aca="false">IF(SWOT!G19="","",SWOT!G19)</f>
         <v/>
       </c>
-      <c r="R9" s="50" t="str">
+      <c r="R9" s="51" t="str">
         <f aca="false">IF(Q9="","",RANK(Q9,$Q$6:$Q$37)+COUNTIF($Q$5:Q8,Q9))</f>
         <v/>
       </c>
@@ -4115,11 +4155,11 @@
       <c r="B10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="44" t="str">
+      <c r="C10" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B10,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="48" t="str">
+      <c r="D10" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B10,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4127,11 +4167,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B10,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F10" s="49" t="str">
+      <c r="F10" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B10,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="49" t="str">
+      <c r="G10" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B10,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4139,33 +4179,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B10,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I10" s="49" t="str">
+      <c r="I10" s="50" t="str">
         <f aca="false">IF(H10="","",IF(H10&gt;=15,"Alta",IF(H10&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L10" s="50" t="s">
+      <c r="L10" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="M10" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N10" s="51" t="str">
+      <c r="M10" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N10" s="52" t="str">
         <f aca="false">IF(SWOT!C20="","",SWOT!C20)</f>
         <v/>
       </c>
-      <c r="O10" s="50" t="str">
+      <c r="O10" s="51" t="str">
         <f aca="false">IF(SWOT!E20="","",SWOT!E20)</f>
         <v/>
       </c>
-      <c r="P10" s="50" t="str">
+      <c r="P10" s="51" t="str">
         <f aca="false">IF(SWOT!F20="","",SWOT!F20)</f>
         <v/>
       </c>
-      <c r="Q10" s="50" t="str">
+      <c r="Q10" s="51" t="str">
         <f aca="false">IF(SWOT!G20="","",SWOT!G20)</f>
         <v/>
       </c>
-      <c r="R10" s="50" t="str">
+      <c r="R10" s="51" t="str">
         <f aca="false">IF(Q10="","",RANK(Q10,$Q$6:$Q$37)+COUNTIF($Q$5:Q9,Q10))</f>
         <v/>
       </c>
@@ -4174,11 +4214,11 @@
       <c r="B11" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="44" t="str">
+      <c r="C11" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B11,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="48" t="str">
+      <c r="D11" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B11,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4186,11 +4226,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B11,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F11" s="49" t="str">
+      <c r="F11" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B11,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="49" t="str">
+      <c r="G11" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B11,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4198,33 +4238,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B11,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I11" s="49" t="str">
+      <c r="I11" s="50" t="str">
         <f aca="false">IF(H11="","",IF(H11&gt;=15,"Alta",IF(H11&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L11" s="50" t="s">
+      <c r="L11" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="M11" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N11" s="51" t="str">
+      <c r="M11" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N11" s="52" t="str">
         <f aca="false">IF(SWOT!C21="","",SWOT!C21)</f>
         <v/>
       </c>
-      <c r="O11" s="50" t="str">
+      <c r="O11" s="51" t="str">
         <f aca="false">IF(SWOT!E21="","",SWOT!E21)</f>
         <v/>
       </c>
-      <c r="P11" s="50" t="str">
+      <c r="P11" s="51" t="str">
         <f aca="false">IF(SWOT!F21="","",SWOT!F21)</f>
         <v/>
       </c>
-      <c r="Q11" s="50" t="str">
+      <c r="Q11" s="51" t="str">
         <f aca="false">IF(SWOT!G21="","",SWOT!G21)</f>
         <v/>
       </c>
-      <c r="R11" s="50" t="str">
+      <c r="R11" s="51" t="str">
         <f aca="false">IF(Q11="","",RANK(Q11,$Q$6:$Q$37)+COUNTIF($Q$5:Q10,Q11))</f>
         <v/>
       </c>
@@ -4233,11 +4273,11 @@
       <c r="B12" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="44" t="str">
+      <c r="C12" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B12,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D12" s="48" t="str">
+      <c r="D12" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B12,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4245,11 +4285,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B12,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="49" t="str">
+      <c r="F12" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B12,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G12" s="49" t="str">
+      <c r="G12" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B12,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4257,33 +4297,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B12,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I12" s="49" t="str">
+      <c r="I12" s="50" t="str">
         <f aca="false">IF(H12="","",IF(H12&gt;=15,"Alta",IF(H12&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L12" s="50" t="s">
+      <c r="L12" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="M12" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N12" s="51" t="str">
+      <c r="M12" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N12" s="52" t="str">
         <f aca="false">IF(SWOT!C22="","",SWOT!C22)</f>
         <v/>
       </c>
-      <c r="O12" s="50" t="str">
+      <c r="O12" s="51" t="str">
         <f aca="false">IF(SWOT!E22="","",SWOT!E22)</f>
         <v/>
       </c>
-      <c r="P12" s="50" t="str">
+      <c r="P12" s="51" t="str">
         <f aca="false">IF(SWOT!F22="","",SWOT!F22)</f>
         <v/>
       </c>
-      <c r="Q12" s="50" t="str">
+      <c r="Q12" s="51" t="str">
         <f aca="false">IF(SWOT!G22="","",SWOT!G22)</f>
         <v/>
       </c>
-      <c r="R12" s="50" t="str">
+      <c r="R12" s="51" t="str">
         <f aca="false">IF(Q12="","",RANK(Q12,$Q$6:$Q$37)+COUNTIF($Q$5:Q11,Q12))</f>
         <v/>
       </c>
@@ -4292,11 +4332,11 @@
       <c r="B13" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="44" t="str">
+      <c r="C13" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B13,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D13" s="48" t="str">
+      <c r="D13" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B13,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4304,11 +4344,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B13,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F13" s="49" t="str">
+      <c r="F13" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B13,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G13" s="49" t="str">
+      <c r="G13" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B13,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4316,33 +4356,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B13,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I13" s="49" t="str">
+      <c r="I13" s="50" t="str">
         <f aca="false">IF(H13="","",IF(H13&gt;=15,"Alta",IF(H13&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L13" s="50" t="s">
+      <c r="L13" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="M13" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="N13" s="51" t="str">
+      <c r="M13" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N13" s="52" t="str">
         <f aca="false">IF(SWOT!C23="","",SWOT!C23)</f>
         <v/>
       </c>
-      <c r="O13" s="50" t="str">
+      <c r="O13" s="51" t="str">
         <f aca="false">IF(SWOT!E23="","",SWOT!E23)</f>
         <v/>
       </c>
-      <c r="P13" s="50" t="str">
+      <c r="P13" s="51" t="str">
         <f aca="false">IF(SWOT!F23="","",SWOT!F23)</f>
         <v/>
       </c>
-      <c r="Q13" s="50" t="str">
+      <c r="Q13" s="51" t="str">
         <f aca="false">IF(SWOT!G23="","",SWOT!G23)</f>
         <v/>
       </c>
-      <c r="R13" s="50" t="str">
+      <c r="R13" s="51" t="str">
         <f aca="false">IF(Q13="","",RANK(Q13,$Q$6:$Q$37)+COUNTIF($Q$5:Q12,Q13))</f>
         <v/>
       </c>
@@ -4351,11 +4391,11 @@
       <c r="B14" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="44" t="str">
+      <c r="C14" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B14,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D14" s="48" t="str">
+      <c r="D14" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B14,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4363,11 +4403,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B14,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F14" s="49" t="str">
+      <c r="F14" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B14,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G14" s="49" t="str">
+      <c r="G14" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B14,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4375,33 +4415,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B14,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I14" s="49" t="str">
+      <c r="I14" s="50" t="str">
         <f aca="false">IF(H14="","",IF(H14&gt;=15,"Alta",IF(H14&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L14" s="50" t="s">
+      <c r="L14" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="M14" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N14" s="51" t="str">
+      <c r="M14" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N14" s="52" t="str">
         <f aca="false">IF(SWOT!I16="","",SWOT!I16)</f>
         <v/>
       </c>
-      <c r="O14" s="50" t="str">
+      <c r="O14" s="51" t="str">
         <f aca="false">IF(SWOT!K16="","",SWOT!K16)</f>
         <v/>
       </c>
-      <c r="P14" s="50" t="str">
+      <c r="P14" s="51" t="str">
         <f aca="false">IF(SWOT!L16="","",SWOT!L16)</f>
         <v/>
       </c>
-      <c r="Q14" s="50" t="str">
+      <c r="Q14" s="51" t="str">
         <f aca="false">IF(SWOT!M16="","",SWOT!M16)</f>
         <v/>
       </c>
-      <c r="R14" s="50" t="str">
+      <c r="R14" s="51" t="str">
         <f aca="false">IF(Q14="","",RANK(Q14,$Q$6:$Q$37)+COUNTIF($Q$5:Q13,Q14))</f>
         <v/>
       </c>
@@ -4410,11 +4450,11 @@
       <c r="B15" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="44" t="str">
+      <c r="C15" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B15,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="48" t="str">
+      <c r="D15" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B15,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4422,11 +4462,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B15,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="49" t="str">
+      <c r="F15" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B15,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="49" t="str">
+      <c r="G15" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B15,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4434,33 +4474,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B15,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I15" s="49" t="str">
+      <c r="I15" s="50" t="str">
         <f aca="false">IF(H15="","",IF(H15&gt;=15,"Alta",IF(H15&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L15" s="50" t="s">
+      <c r="L15" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N15" s="51" t="str">
+      <c r="M15" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N15" s="52" t="str">
         <f aca="false">IF(SWOT!I17="","",SWOT!I17)</f>
         <v/>
       </c>
-      <c r="O15" s="50" t="str">
+      <c r="O15" s="51" t="str">
         <f aca="false">IF(SWOT!K17="","",SWOT!K17)</f>
         <v/>
       </c>
-      <c r="P15" s="50" t="str">
+      <c r="P15" s="51" t="str">
         <f aca="false">IF(SWOT!L17="","",SWOT!L17)</f>
         <v/>
       </c>
-      <c r="Q15" s="50" t="str">
+      <c r="Q15" s="51" t="str">
         <f aca="false">IF(SWOT!M17="","",SWOT!M17)</f>
         <v/>
       </c>
-      <c r="R15" s="50" t="str">
+      <c r="R15" s="51" t="str">
         <f aca="false">IF(Q15="","",RANK(Q15,$Q$6:$Q$37)+COUNTIF($Q$5:Q14,Q15))</f>
         <v/>
       </c>
@@ -4469,11 +4509,11 @@
       <c r="B16" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="44" t="str">
+      <c r="C16" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B16,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="48" t="str">
+      <c r="D16" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B16,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4481,11 +4521,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B16,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="49" t="str">
+      <c r="F16" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B16,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="49" t="str">
+      <c r="G16" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B16,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4493,33 +4533,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B16,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I16" s="49" t="str">
+      <c r="I16" s="50" t="str">
         <f aca="false">IF(H16="","",IF(H16&gt;=15,"Alta",IF(H16&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L16" s="50" t="s">
+      <c r="L16" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="M16" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N16" s="51" t="str">
+      <c r="M16" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N16" s="52" t="str">
         <f aca="false">IF(SWOT!I18="","",SWOT!I18)</f>
         <v/>
       </c>
-      <c r="O16" s="50" t="str">
+      <c r="O16" s="51" t="str">
         <f aca="false">IF(SWOT!K18="","",SWOT!K18)</f>
         <v/>
       </c>
-      <c r="P16" s="50" t="str">
+      <c r="P16" s="51" t="str">
         <f aca="false">IF(SWOT!L18="","",SWOT!L18)</f>
         <v/>
       </c>
-      <c r="Q16" s="50" t="str">
+      <c r="Q16" s="51" t="str">
         <f aca="false">IF(SWOT!M18="","",SWOT!M18)</f>
         <v/>
       </c>
-      <c r="R16" s="50" t="str">
+      <c r="R16" s="51" t="str">
         <f aca="false">IF(Q16="","",RANK(Q16,$Q$6:$Q$37)+COUNTIF($Q$5:Q15,Q16))</f>
         <v/>
       </c>
@@ -4528,11 +4568,11 @@
       <c r="B17" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C17" s="44" t="str">
+      <c r="C17" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B17,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="48" t="str">
+      <c r="D17" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B17,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4540,11 +4580,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B17,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="49" t="str">
+      <c r="F17" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B17,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="49" t="str">
+      <c r="G17" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B17,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4552,33 +4592,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B17,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I17" s="49" t="str">
+      <c r="I17" s="50" t="str">
         <f aca="false">IF(H17="","",IF(H17&gt;=15,"Alta",IF(H17&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L17" s="50" t="s">
+      <c r="L17" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="M17" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N17" s="51" t="str">
+      <c r="M17" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N17" s="52" t="str">
         <f aca="false">IF(SWOT!I19="","",SWOT!I19)</f>
         <v/>
       </c>
-      <c r="O17" s="50" t="str">
+      <c r="O17" s="51" t="str">
         <f aca="false">IF(SWOT!K19="","",SWOT!K19)</f>
         <v/>
       </c>
-      <c r="P17" s="50" t="str">
+      <c r="P17" s="51" t="str">
         <f aca="false">IF(SWOT!L19="","",SWOT!L19)</f>
         <v/>
       </c>
-      <c r="Q17" s="50" t="str">
+      <c r="Q17" s="51" t="str">
         <f aca="false">IF(SWOT!M19="","",SWOT!M19)</f>
         <v/>
       </c>
-      <c r="R17" s="50" t="str">
+      <c r="R17" s="51" t="str">
         <f aca="false">IF(Q17="","",RANK(Q17,$Q$6:$Q$37)+COUNTIF($Q$5:Q16,Q17))</f>
         <v/>
       </c>
@@ -4587,11 +4627,11 @@
       <c r="B18" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="C18" s="44" t="str">
+      <c r="C18" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B18,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="48" t="str">
+      <c r="D18" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B18,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4599,11 +4639,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B18,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="49" t="str">
+      <c r="F18" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B18,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="49" t="str">
+      <c r="G18" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B18,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4611,33 +4651,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B18,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I18" s="49" t="str">
+      <c r="I18" s="50" t="str">
         <f aca="false">IF(H18="","",IF(H18&gt;=15,"Alta",IF(H18&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L18" s="50" t="s">
+      <c r="L18" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="M18" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N18" s="51" t="str">
+      <c r="M18" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N18" s="52" t="str">
         <f aca="false">IF(SWOT!I20="","",SWOT!I20)</f>
         <v/>
       </c>
-      <c r="O18" s="50" t="str">
+      <c r="O18" s="51" t="str">
         <f aca="false">IF(SWOT!K20="","",SWOT!K20)</f>
         <v/>
       </c>
-      <c r="P18" s="50" t="str">
+      <c r="P18" s="51" t="str">
         <f aca="false">IF(SWOT!L20="","",SWOT!L20)</f>
         <v/>
       </c>
-      <c r="Q18" s="50" t="str">
+      <c r="Q18" s="51" t="str">
         <f aca="false">IF(SWOT!M20="","",SWOT!M20)</f>
         <v/>
       </c>
-      <c r="R18" s="50" t="str">
+      <c r="R18" s="51" t="str">
         <f aca="false">IF(Q18="","",RANK(Q18,$Q$6:$Q$37)+COUNTIF($Q$5:Q17,Q18))</f>
         <v/>
       </c>
@@ -4646,11 +4686,11 @@
       <c r="B19" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="44" t="str">
+      <c r="C19" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B19,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="48" t="str">
+      <c r="D19" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B19,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4658,11 +4698,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B19,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F19" s="49" t="str">
+      <c r="F19" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B19,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="49" t="str">
+      <c r="G19" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B19,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4670,33 +4710,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B19,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="49" t="str">
+      <c r="I19" s="50" t="str">
         <f aca="false">IF(H19="","",IF(H19&gt;=15,"Alta",IF(H19&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L19" s="50" t="s">
+      <c r="L19" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="M19" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N19" s="51" t="str">
+      <c r="M19" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N19" s="52" t="str">
         <f aca="false">IF(SWOT!I21="","",SWOT!I21)</f>
         <v/>
       </c>
-      <c r="O19" s="50" t="str">
+      <c r="O19" s="51" t="str">
         <f aca="false">IF(SWOT!K21="","",SWOT!K21)</f>
         <v/>
       </c>
-      <c r="P19" s="50" t="str">
+      <c r="P19" s="51" t="str">
         <f aca="false">IF(SWOT!L21="","",SWOT!L21)</f>
         <v/>
       </c>
-      <c r="Q19" s="50" t="str">
+      <c r="Q19" s="51" t="str">
         <f aca="false">IF(SWOT!M21="","",SWOT!M21)</f>
         <v/>
       </c>
-      <c r="R19" s="50" t="str">
+      <c r="R19" s="51" t="str">
         <f aca="false">IF(Q19="","",RANK(Q19,$Q$6:$Q$37)+COUNTIF($Q$5:Q18,Q19))</f>
         <v/>
       </c>
@@ -4705,11 +4745,11 @@
       <c r="B20" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="C20" s="44" t="str">
+      <c r="C20" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B20,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="48" t="str">
+      <c r="D20" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B20,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4717,11 +4757,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B20,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="49" t="str">
+      <c r="F20" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B20,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="49" t="str">
+      <c r="G20" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B20,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4729,33 +4769,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B20,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="49" t="str">
+      <c r="I20" s="50" t="str">
         <f aca="false">IF(H20="","",IF(H20&gt;=15,"Alta",IF(H20&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L20" s="50" t="s">
+      <c r="L20" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="M20" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N20" s="51" t="str">
+      <c r="M20" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N20" s="52" t="str">
         <f aca="false">IF(SWOT!I22="","",SWOT!I22)</f>
         <v/>
       </c>
-      <c r="O20" s="50" t="str">
+      <c r="O20" s="51" t="str">
         <f aca="false">IF(SWOT!K22="","",SWOT!K22)</f>
         <v/>
       </c>
-      <c r="P20" s="50" t="str">
+      <c r="P20" s="51" t="str">
         <f aca="false">IF(SWOT!L22="","",SWOT!L22)</f>
         <v/>
       </c>
-      <c r="Q20" s="50" t="str">
+      <c r="Q20" s="51" t="str">
         <f aca="false">IF(SWOT!M22="","",SWOT!M22)</f>
         <v/>
       </c>
-      <c r="R20" s="50" t="str">
+      <c r="R20" s="51" t="str">
         <f aca="false">IF(Q20="","",RANK(Q20,$Q$6:$Q$37)+COUNTIF($Q$5:Q19,Q20))</f>
         <v/>
       </c>
@@ -4764,11 +4804,11 @@
       <c r="B21" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="C21" s="44" t="str">
+      <c r="C21" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B21,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="48" t="str">
+      <c r="D21" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B21,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4776,11 +4816,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B21,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="49" t="str">
+      <c r="F21" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B21,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="49" t="str">
+      <c r="G21" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B21,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4788,33 +4828,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B21,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="49" t="str">
+      <c r="I21" s="50" t="str">
         <f aca="false">IF(H21="","",IF(H21&gt;=15,"Alta",IF(H21&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L21" s="50" t="s">
+      <c r="L21" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="M21" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="N21" s="51" t="str">
+      <c r="M21" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="N21" s="52" t="str">
         <f aca="false">IF(SWOT!I23="","",SWOT!I23)</f>
         <v/>
       </c>
-      <c r="O21" s="50" t="str">
+      <c r="O21" s="51" t="str">
         <f aca="false">IF(SWOT!K23="","",SWOT!K23)</f>
         <v/>
       </c>
-      <c r="P21" s="50" t="str">
+      <c r="P21" s="51" t="str">
         <f aca="false">IF(SWOT!L23="","",SWOT!L23)</f>
         <v/>
       </c>
-      <c r="Q21" s="50" t="str">
+      <c r="Q21" s="51" t="str">
         <f aca="false">IF(SWOT!M23="","",SWOT!M23)</f>
         <v/>
       </c>
-      <c r="R21" s="50" t="str">
+      <c r="R21" s="51" t="str">
         <f aca="false">IF(Q21="","",RANK(Q21,$Q$6:$Q$37)+COUNTIF($Q$5:Q20,Q21))</f>
         <v/>
       </c>
@@ -4823,11 +4863,11 @@
       <c r="B22" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="C22" s="44" t="str">
+      <c r="C22" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B22,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D22" s="48" t="str">
+      <c r="D22" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B22,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4835,11 +4875,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B22,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F22" s="49" t="str">
+      <c r="F22" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B22,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G22" s="49" t="str">
+      <c r="G22" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B22,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4847,33 +4887,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B22,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="49" t="str">
+      <c r="I22" s="50" t="str">
         <f aca="false">IF(H22="","",IF(H22&gt;=15,"Alta",IF(H22&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L22" s="50" t="s">
+      <c r="L22" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="M22" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N22" s="51" t="str">
+      <c r="M22" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N22" s="52" t="str">
         <f aca="false">IF(SWOT!C30="","",SWOT!C30)</f>
         <v/>
       </c>
-      <c r="O22" s="50" t="str">
+      <c r="O22" s="51" t="str">
         <f aca="false">IF(SWOT!E30="","",SWOT!E30)</f>
         <v/>
       </c>
-      <c r="P22" s="50" t="str">
+      <c r="P22" s="51" t="str">
         <f aca="false">IF(SWOT!F30="","",SWOT!F30)</f>
         <v/>
       </c>
-      <c r="Q22" s="50" t="str">
+      <c r="Q22" s="51" t="str">
         <f aca="false">IF(SWOT!G30="","",SWOT!G30)</f>
         <v/>
       </c>
-      <c r="R22" s="50" t="str">
+      <c r="R22" s="51" t="str">
         <f aca="false">IF(Q22="","",RANK(Q22,$Q$6:$Q$37)+COUNTIF($Q$5:Q21,Q22))</f>
         <v/>
       </c>
@@ -4882,11 +4922,11 @@
       <c r="B23" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="C23" s="44" t="str">
+      <c r="C23" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B23,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="48" t="str">
+      <c r="D23" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B23,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4894,11 +4934,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B23,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F23" s="49" t="str">
+      <c r="F23" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B23,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="49" t="str">
+      <c r="G23" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B23,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4906,33 +4946,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B23,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="49" t="str">
+      <c r="I23" s="50" t="str">
         <f aca="false">IF(H23="","",IF(H23&gt;=15,"Alta",IF(H23&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L23" s="50" t="s">
+      <c r="L23" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="M23" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N23" s="51" t="str">
+      <c r="M23" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="52" t="str">
         <f aca="false">IF(SWOT!C31="","",SWOT!C31)</f>
         <v/>
       </c>
-      <c r="O23" s="50" t="str">
+      <c r="O23" s="51" t="str">
         <f aca="false">IF(SWOT!E31="","",SWOT!E31)</f>
         <v/>
       </c>
-      <c r="P23" s="50" t="str">
+      <c r="P23" s="51" t="str">
         <f aca="false">IF(SWOT!F31="","",SWOT!F31)</f>
         <v/>
       </c>
-      <c r="Q23" s="50" t="str">
+      <c r="Q23" s="51" t="str">
         <f aca="false">IF(SWOT!G31="","",SWOT!G31)</f>
         <v/>
       </c>
-      <c r="R23" s="50" t="str">
+      <c r="R23" s="51" t="str">
         <f aca="false">IF(Q23="","",RANK(Q23,$Q$6:$Q$37)+COUNTIF($Q$5:Q22,Q23))</f>
         <v/>
       </c>
@@ -4941,11 +4981,11 @@
       <c r="B24" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C24" s="44" t="str">
+      <c r="C24" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B24,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="48" t="str">
+      <c r="D24" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B24,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4953,11 +4993,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B24,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F24" s="49" t="str">
+      <c r="F24" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B24,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="49" t="str">
+      <c r="G24" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B24,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -4965,33 +5005,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B24,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="49" t="str">
+      <c r="I24" s="50" t="str">
         <f aca="false">IF(H24="","",IF(H24&gt;=15,"Alta",IF(H24&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L24" s="50" t="s">
+      <c r="L24" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="M24" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N24" s="51" t="str">
+      <c r="M24" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N24" s="52" t="str">
         <f aca="false">IF(SWOT!C32="","",SWOT!C32)</f>
         <v/>
       </c>
-      <c r="O24" s="50" t="str">
+      <c r="O24" s="51" t="str">
         <f aca="false">IF(SWOT!E32="","",SWOT!E32)</f>
         <v/>
       </c>
-      <c r="P24" s="50" t="str">
+      <c r="P24" s="51" t="str">
         <f aca="false">IF(SWOT!F32="","",SWOT!F32)</f>
         <v/>
       </c>
-      <c r="Q24" s="50" t="str">
+      <c r="Q24" s="51" t="str">
         <f aca="false">IF(SWOT!G32="","",SWOT!G32)</f>
         <v/>
       </c>
-      <c r="R24" s="50" t="str">
+      <c r="R24" s="51" t="str">
         <f aca="false">IF(Q24="","",RANK(Q24,$Q$6:$Q$37)+COUNTIF($Q$5:Q23,Q24))</f>
         <v/>
       </c>
@@ -5000,11 +5040,11 @@
       <c r="B25" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C25" s="44" t="str">
+      <c r="C25" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B25,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="48" t="str">
+      <c r="D25" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B25,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5012,11 +5052,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B25,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="49" t="str">
+      <c r="F25" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B25,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="49" t="str">
+      <c r="G25" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B25,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5024,33 +5064,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B25,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="49" t="str">
+      <c r="I25" s="50" t="str">
         <f aca="false">IF(H25="","",IF(H25&gt;=15,"Alta",IF(H25&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L25" s="50" t="s">
+      <c r="L25" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="M25" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N25" s="51" t="str">
+      <c r="M25" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N25" s="52" t="str">
         <f aca="false">IF(SWOT!C33="","",SWOT!C33)</f>
         <v/>
       </c>
-      <c r="O25" s="50" t="str">
+      <c r="O25" s="51" t="str">
         <f aca="false">IF(SWOT!E33="","",SWOT!E33)</f>
         <v/>
       </c>
-      <c r="P25" s="50" t="str">
+      <c r="P25" s="51" t="str">
         <f aca="false">IF(SWOT!F33="","",SWOT!F33)</f>
         <v/>
       </c>
-      <c r="Q25" s="50" t="str">
+      <c r="Q25" s="51" t="str">
         <f aca="false">IF(SWOT!G33="","",SWOT!G33)</f>
         <v/>
       </c>
-      <c r="R25" s="50" t="str">
+      <c r="R25" s="51" t="str">
         <f aca="false">IF(Q25="","",RANK(Q25,$Q$6:$Q$37)+COUNTIF($Q$5:Q24,Q25))</f>
         <v/>
       </c>
@@ -5059,11 +5099,11 @@
       <c r="B26" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="C26" s="44" t="str">
+      <c r="C26" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B26,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="48" t="str">
+      <c r="D26" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B26,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5071,11 +5111,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B26,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F26" s="49" t="str">
+      <c r="F26" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B26,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="49" t="str">
+      <c r="G26" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B26,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5083,33 +5123,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B26,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="49" t="str">
+      <c r="I26" s="50" t="str">
         <f aca="false">IF(H26="","",IF(H26&gt;=15,"Alta",IF(H26&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L26" s="50" t="s">
+      <c r="L26" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="M26" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N26" s="51" t="str">
+      <c r="M26" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N26" s="52" t="str">
         <f aca="false">IF(SWOT!C34="","",SWOT!C34)</f>
         <v/>
       </c>
-      <c r="O26" s="50" t="str">
+      <c r="O26" s="51" t="str">
         <f aca="false">IF(SWOT!E34="","",SWOT!E34)</f>
         <v/>
       </c>
-      <c r="P26" s="50" t="str">
+      <c r="P26" s="51" t="str">
         <f aca="false">IF(SWOT!F34="","",SWOT!F34)</f>
         <v/>
       </c>
-      <c r="Q26" s="50" t="str">
+      <c r="Q26" s="51" t="str">
         <f aca="false">IF(SWOT!G34="","",SWOT!G34)</f>
         <v/>
       </c>
-      <c r="R26" s="50" t="str">
+      <c r="R26" s="51" t="str">
         <f aca="false">IF(Q26="","",RANK(Q26,$Q$6:$Q$37)+COUNTIF($Q$5:Q25,Q26))</f>
         <v/>
       </c>
@@ -5118,11 +5158,11 @@
       <c r="B27" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="C27" s="44" t="str">
+      <c r="C27" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B27,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D27" s="48" t="str">
+      <c r="D27" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B27,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5130,11 +5170,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B27,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F27" s="49" t="str">
+      <c r="F27" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B27,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="49" t="str">
+      <c r="G27" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B27,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5142,33 +5182,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B27,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="49" t="str">
+      <c r="I27" s="50" t="str">
         <f aca="false">IF(H27="","",IF(H27&gt;=15,"Alta",IF(H27&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L27" s="50" t="s">
+      <c r="L27" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="M27" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N27" s="51" t="str">
+      <c r="M27" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N27" s="52" t="str">
         <f aca="false">IF(SWOT!C35="","",SWOT!C35)</f>
         <v/>
       </c>
-      <c r="O27" s="50" t="str">
+      <c r="O27" s="51" t="str">
         <f aca="false">IF(SWOT!E35="","",SWOT!E35)</f>
         <v/>
       </c>
-      <c r="P27" s="50" t="str">
+      <c r="P27" s="51" t="str">
         <f aca="false">IF(SWOT!F35="","",SWOT!F35)</f>
         <v/>
       </c>
-      <c r="Q27" s="50" t="str">
+      <c r="Q27" s="51" t="str">
         <f aca="false">IF(SWOT!G35="","",SWOT!G35)</f>
         <v/>
       </c>
-      <c r="R27" s="50" t="str">
+      <c r="R27" s="51" t="str">
         <f aca="false">IF(Q27="","",RANK(Q27,$Q$6:$Q$37)+COUNTIF($Q$5:Q26,Q27))</f>
         <v/>
       </c>
@@ -5177,11 +5217,11 @@
       <c r="B28" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="C28" s="44" t="str">
+      <c r="C28" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B28,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D28" s="48" t="str">
+      <c r="D28" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B28,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5189,11 +5229,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B28,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F28" s="49" t="str">
+      <c r="F28" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B28,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G28" s="49" t="str">
+      <c r="G28" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B28,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5201,33 +5241,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B28,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="49" t="str">
+      <c r="I28" s="50" t="str">
         <f aca="false">IF(H28="","",IF(H28&gt;=15,"Alta",IF(H28&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L28" s="50" t="s">
+      <c r="L28" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="M28" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N28" s="51" t="str">
+      <c r="M28" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N28" s="52" t="str">
         <f aca="false">IF(SWOT!C36="","",SWOT!C36)</f>
         <v/>
       </c>
-      <c r="O28" s="50" t="str">
+      <c r="O28" s="51" t="str">
         <f aca="false">IF(SWOT!E36="","",SWOT!E36)</f>
         <v/>
       </c>
-      <c r="P28" s="50" t="str">
+      <c r="P28" s="51" t="str">
         <f aca="false">IF(SWOT!F36="","",SWOT!F36)</f>
         <v/>
       </c>
-      <c r="Q28" s="50" t="str">
+      <c r="Q28" s="51" t="str">
         <f aca="false">IF(SWOT!G36="","",SWOT!G36)</f>
         <v/>
       </c>
-      <c r="R28" s="50" t="str">
+      <c r="R28" s="51" t="str">
         <f aca="false">IF(Q28="","",RANK(Q28,$Q$6:$Q$37)+COUNTIF($Q$5:Q27,Q28))</f>
         <v/>
       </c>
@@ -5236,11 +5276,11 @@
       <c r="B29" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="C29" s="44" t="str">
+      <c r="C29" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B29,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D29" s="48" t="str">
+      <c r="D29" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B29,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5248,11 +5288,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B29,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F29" s="49" t="str">
+      <c r="F29" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B29,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G29" s="49" t="str">
+      <c r="G29" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B29,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5260,33 +5300,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B29,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="49" t="str">
+      <c r="I29" s="50" t="str">
         <f aca="false">IF(H29="","",IF(H29&gt;=15,"Alta",IF(H29&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L29" s="50" t="s">
+      <c r="L29" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="M29" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="N29" s="51" t="str">
+      <c r="M29" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="N29" s="52" t="str">
         <f aca="false">IF(SWOT!C37="","",SWOT!C37)</f>
         <v/>
       </c>
-      <c r="O29" s="50" t="str">
+      <c r="O29" s="51" t="str">
         <f aca="false">IF(SWOT!E37="","",SWOT!E37)</f>
         <v/>
       </c>
-      <c r="P29" s="50" t="str">
+      <c r="P29" s="51" t="str">
         <f aca="false">IF(SWOT!F37="","",SWOT!F37)</f>
         <v/>
       </c>
-      <c r="Q29" s="50" t="str">
+      <c r="Q29" s="51" t="str">
         <f aca="false">IF(SWOT!G37="","",SWOT!G37)</f>
         <v/>
       </c>
-      <c r="R29" s="50" t="str">
+      <c r="R29" s="51" t="str">
         <f aca="false">IF(Q29="","",RANK(Q29,$Q$6:$Q$37)+COUNTIF($Q$5:Q28,Q29))</f>
         <v/>
       </c>
@@ -5295,11 +5335,11 @@
       <c r="B30" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="44" t="str">
+      <c r="C30" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B30,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D30" s="48" t="str">
+      <c r="D30" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B30,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5307,11 +5347,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B30,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F30" s="49" t="str">
+      <c r="F30" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B30,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G30" s="49" t="str">
+      <c r="G30" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B30,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5319,33 +5359,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B30,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="49" t="str">
+      <c r="I30" s="50" t="str">
         <f aca="false">IF(H30="","",IF(H30&gt;=15,"Alta",IF(H30&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L30" s="50" t="s">
+      <c r="L30" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="M30" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N30" s="51" t="str">
+      <c r="M30" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N30" s="52" t="str">
         <f aca="false">IF(SWOT!I30="","",SWOT!I30)</f>
         <v/>
       </c>
-      <c r="O30" s="50" t="str">
+      <c r="O30" s="51" t="str">
         <f aca="false">IF(SWOT!K30="","",SWOT!K30)</f>
         <v/>
       </c>
-      <c r="P30" s="50" t="str">
+      <c r="P30" s="51" t="str">
         <f aca="false">IF(SWOT!L30="","",SWOT!L30)</f>
         <v/>
       </c>
-      <c r="Q30" s="50" t="str">
+      <c r="Q30" s="51" t="str">
         <f aca="false">IF(SWOT!M30="","",SWOT!M30)</f>
         <v/>
       </c>
-      <c r="R30" s="50" t="str">
+      <c r="R30" s="51" t="str">
         <f aca="false">IF(Q30="","",RANK(Q30,$Q$6:$Q$37)+COUNTIF($Q$5:Q29,Q30))</f>
         <v/>
       </c>
@@ -5354,11 +5394,11 @@
       <c r="B31" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="C31" s="44" t="str">
+      <c r="C31" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B31,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="48" t="str">
+      <c r="D31" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B31,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5366,11 +5406,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B31,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="49" t="str">
+      <c r="F31" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B31,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="49" t="str">
+      <c r="G31" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B31,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5378,33 +5418,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B31,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="49" t="str">
+      <c r="I31" s="50" t="str">
         <f aca="false">IF(H31="","",IF(H31&gt;=15,"Alta",IF(H31&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L31" s="50" t="s">
+      <c r="L31" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="M31" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N31" s="51" t="str">
+      <c r="M31" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N31" s="52" t="str">
         <f aca="false">IF(SWOT!I31="","",SWOT!I31)</f>
         <v/>
       </c>
-      <c r="O31" s="50" t="str">
+      <c r="O31" s="51" t="str">
         <f aca="false">IF(SWOT!K31="","",SWOT!K31)</f>
         <v/>
       </c>
-      <c r="P31" s="50" t="str">
+      <c r="P31" s="51" t="str">
         <f aca="false">IF(SWOT!L31="","",SWOT!L31)</f>
         <v/>
       </c>
-      <c r="Q31" s="50" t="str">
+      <c r="Q31" s="51" t="str">
         <f aca="false">IF(SWOT!M31="","",SWOT!M31)</f>
         <v/>
       </c>
-      <c r="R31" s="50" t="str">
+      <c r="R31" s="51" t="str">
         <f aca="false">IF(Q31="","",RANK(Q31,$Q$6:$Q$37)+COUNTIF($Q$5:Q30,Q31))</f>
         <v/>
       </c>
@@ -5413,11 +5453,11 @@
       <c r="B32" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="C32" s="44" t="str">
+      <c r="C32" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B32,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="48" t="str">
+      <c r="D32" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B32,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5425,11 +5465,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B32,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="49" t="str">
+      <c r="F32" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B32,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="49" t="str">
+      <c r="G32" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B32,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5437,33 +5477,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B32,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="49" t="str">
+      <c r="I32" s="50" t="str">
         <f aca="false">IF(H32="","",IF(H32&gt;=15,"Alta",IF(H32&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L32" s="50" t="s">
+      <c r="L32" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="M32" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N32" s="51" t="str">
+      <c r="M32" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N32" s="52" t="str">
         <f aca="false">IF(SWOT!I32="","",SWOT!I32)</f>
         <v/>
       </c>
-      <c r="O32" s="50" t="str">
+      <c r="O32" s="51" t="str">
         <f aca="false">IF(SWOT!K32="","",SWOT!K32)</f>
         <v/>
       </c>
-      <c r="P32" s="50" t="str">
+      <c r="P32" s="51" t="str">
         <f aca="false">IF(SWOT!L32="","",SWOT!L32)</f>
         <v/>
       </c>
-      <c r="Q32" s="50" t="str">
+      <c r="Q32" s="51" t="str">
         <f aca="false">IF(SWOT!M32="","",SWOT!M32)</f>
         <v/>
       </c>
-      <c r="R32" s="50" t="str">
+      <c r="R32" s="51" t="str">
         <f aca="false">IF(Q32="","",RANK(Q32,$Q$6:$Q$37)+COUNTIF($Q$5:Q31,Q32))</f>
         <v/>
       </c>
@@ -5472,11 +5512,11 @@
       <c r="B33" s="27" t="n">
         <v>28</v>
       </c>
-      <c r="C33" s="44" t="str">
+      <c r="C33" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B33,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="48" t="str">
+      <c r="D33" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B33,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5484,11 +5524,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B33,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="49" t="str">
+      <c r="F33" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B33,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="49" t="str">
+      <c r="G33" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B33,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5496,33 +5536,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B33,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="49" t="str">
+      <c r="I33" s="50" t="str">
         <f aca="false">IF(H33="","",IF(H33&gt;=15,"Alta",IF(H33&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L33" s="50" t="s">
+      <c r="L33" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="M33" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N33" s="51" t="str">
+      <c r="M33" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N33" s="52" t="str">
         <f aca="false">IF(SWOT!I33="","",SWOT!I33)</f>
         <v/>
       </c>
-      <c r="O33" s="50" t="str">
+      <c r="O33" s="51" t="str">
         <f aca="false">IF(SWOT!K33="","",SWOT!K33)</f>
         <v/>
       </c>
-      <c r="P33" s="50" t="str">
+      <c r="P33" s="51" t="str">
         <f aca="false">IF(SWOT!L33="","",SWOT!L33)</f>
         <v/>
       </c>
-      <c r="Q33" s="50" t="str">
+      <c r="Q33" s="51" t="str">
         <f aca="false">IF(SWOT!M33="","",SWOT!M33)</f>
         <v/>
       </c>
-      <c r="R33" s="50" t="str">
+      <c r="R33" s="51" t="str">
         <f aca="false">IF(Q33="","",RANK(Q33,$Q$6:$Q$37)+COUNTIF($Q$5:Q32,Q33))</f>
         <v/>
       </c>
@@ -5531,11 +5571,11 @@
       <c r="B34" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="C34" s="44" t="str">
+      <c r="C34" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B34,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="48" t="str">
+      <c r="D34" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B34,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5543,11 +5583,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B34,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="49" t="str">
+      <c r="F34" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B34,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="49" t="str">
+      <c r="G34" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B34,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5555,33 +5595,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B34,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="49" t="str">
+      <c r="I34" s="50" t="str">
         <f aca="false">IF(H34="","",IF(H34&gt;=15,"Alta",IF(H34&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L34" s="50" t="s">
+      <c r="L34" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="M34" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N34" s="51" t="str">
+      <c r="M34" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N34" s="52" t="str">
         <f aca="false">IF(SWOT!I34="","",SWOT!I34)</f>
         <v/>
       </c>
-      <c r="O34" s="50" t="str">
+      <c r="O34" s="51" t="str">
         <f aca="false">IF(SWOT!K34="","",SWOT!K34)</f>
         <v/>
       </c>
-      <c r="P34" s="50" t="str">
+      <c r="P34" s="51" t="str">
         <f aca="false">IF(SWOT!L34="","",SWOT!L34)</f>
         <v/>
       </c>
-      <c r="Q34" s="50" t="str">
+      <c r="Q34" s="51" t="str">
         <f aca="false">IF(SWOT!M34="","",SWOT!M34)</f>
         <v/>
       </c>
-      <c r="R34" s="50" t="str">
+      <c r="R34" s="51" t="str">
         <f aca="false">IF(Q34="","",RANK(Q34,$Q$6:$Q$37)+COUNTIF($Q$5:Q33,Q34))</f>
         <v/>
       </c>
@@ -5590,11 +5630,11 @@
       <c r="B35" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="C35" s="44" t="str">
+      <c r="C35" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B35,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="48" t="str">
+      <c r="D35" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B35,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5602,11 +5642,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B35,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="49" t="str">
+      <c r="F35" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B35,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="49" t="str">
+      <c r="G35" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B35,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5614,33 +5654,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B35,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="49" t="str">
+      <c r="I35" s="50" t="str">
         <f aca="false">IF(H35="","",IF(H35&gt;=15,"Alta",IF(H35&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L35" s="50" t="s">
+      <c r="L35" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="M35" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N35" s="51" t="str">
+      <c r="M35" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N35" s="52" t="str">
         <f aca="false">IF(SWOT!I35="","",SWOT!I35)</f>
         <v/>
       </c>
-      <c r="O35" s="50" t="str">
+      <c r="O35" s="51" t="str">
         <f aca="false">IF(SWOT!K35="","",SWOT!K35)</f>
         <v/>
       </c>
-      <c r="P35" s="50" t="str">
+      <c r="P35" s="51" t="str">
         <f aca="false">IF(SWOT!L35="","",SWOT!L35)</f>
         <v/>
       </c>
-      <c r="Q35" s="50" t="str">
+      <c r="Q35" s="51" t="str">
         <f aca="false">IF(SWOT!M35="","",SWOT!M35)</f>
         <v/>
       </c>
-      <c r="R35" s="50" t="str">
+      <c r="R35" s="51" t="str">
         <f aca="false">IF(Q35="","",RANK(Q35,$Q$6:$Q$37)+COUNTIF($Q$5:Q34,Q35))</f>
         <v/>
       </c>
@@ -5649,11 +5689,11 @@
       <c r="B36" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="C36" s="44" t="str">
+      <c r="C36" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B36,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="48" t="str">
+      <c r="D36" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B36,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5661,11 +5701,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B36,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="49" t="str">
+      <c r="F36" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B36,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="49" t="str">
+      <c r="G36" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B36,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5673,33 +5713,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B36,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="49" t="str">
+      <c r="I36" s="50" t="str">
         <f aca="false">IF(H36="","",IF(H36&gt;=15,"Alta",IF(H36&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L36" s="50" t="s">
+      <c r="L36" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="M36" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N36" s="51" t="str">
+      <c r="M36" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N36" s="52" t="str">
         <f aca="false">IF(SWOT!I36="","",SWOT!I36)</f>
         <v/>
       </c>
-      <c r="O36" s="50" t="str">
+      <c r="O36" s="51" t="str">
         <f aca="false">IF(SWOT!K36="","",SWOT!K36)</f>
         <v/>
       </c>
-      <c r="P36" s="50" t="str">
+      <c r="P36" s="51" t="str">
         <f aca="false">IF(SWOT!L36="","",SWOT!L36)</f>
         <v/>
       </c>
-      <c r="Q36" s="50" t="str">
+      <c r="Q36" s="51" t="str">
         <f aca="false">IF(SWOT!M36="","",SWOT!M36)</f>
         <v/>
       </c>
-      <c r="R36" s="50" t="str">
+      <c r="R36" s="51" t="str">
         <f aca="false">IF(Q36="","",RANK(Q36,$Q$6:$Q$37)+COUNTIF($Q$5:Q35,Q36))</f>
         <v/>
       </c>
@@ -5708,11 +5748,11 @@
       <c r="B37" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="C37" s="44" t="str">
+      <c r="C37" s="45" t="str">
         <f aca="false">IFERROR(INDEX($L$6:$L$37,MATCH($B37,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="48" t="str">
+      <c r="D37" s="49" t="str">
         <f aca="false">IFERROR(INDEX($M$6:$M$37,MATCH($B37,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5720,11 +5760,11 @@
         <f aca="false">IFERROR(INDEX($N$6:$N$37,MATCH($B37,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="49" t="str">
+      <c r="F37" s="50" t="str">
         <f aca="false">IFERROR(INDEX($O$6:$O$37,MATCH($B37,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="49" t="str">
+      <c r="G37" s="50" t="str">
         <f aca="false">IFERROR(INDEX($P$6:$P$37,MATCH($B37,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
@@ -5732,33 +5772,33 @@
         <f aca="false">IFERROR(INDEX($Q$6:$Q$37,MATCH($B37,$R$6:$R$37,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="49" t="str">
+      <c r="I37" s="50" t="str">
         <f aca="false">IF(H37="","",IF(H37&gt;=15,"Alta",IF(H37&gt;=8,"Média","Baixa")))</f>
         <v/>
       </c>
-      <c r="L37" s="50" t="s">
+      <c r="L37" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="M37" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="N37" s="51" t="str">
+      <c r="M37" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="N37" s="52" t="str">
         <f aca="false">IF(SWOT!I37="","",SWOT!I37)</f>
         <v/>
       </c>
-      <c r="O37" s="50" t="str">
+      <c r="O37" s="51" t="str">
         <f aca="false">IF(SWOT!K37="","",SWOT!K37)</f>
         <v/>
       </c>
-      <c r="P37" s="50" t="str">
+      <c r="P37" s="51" t="str">
         <f aca="false">IF(SWOT!L37="","",SWOT!L37)</f>
         <v/>
       </c>
-      <c r="Q37" s="50" t="str">
+      <c r="Q37" s="51" t="str">
         <f aca="false">IF(SWOT!M37="","",SWOT!M37)</f>
         <v/>
       </c>
-      <c r="R37" s="50" t="str">
+      <c r="R37" s="51" t="str">
         <f aca="false">IF(Q37="","",RANK(Q37,$Q$6:$Q$37)+COUNTIF($Q$5:Q36,Q37))</f>
         <v/>
       </c>
@@ -5777,59 +5817,59 @@
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C40" s="39"/>
       <c r="D40" s="39"/>
       <c r="E40" s="39"/>
-      <c r="F40" s="44" t="n">
+      <c r="F40" s="45" t="n">
         <f aca="false">COUNT(H6:H37)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="44"/>
+      <c r="G40" s="45"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="39"/>
       <c r="E41" s="39"/>
-      <c r="F41" s="44" t="n">
+      <c r="F41" s="45" t="n">
         <f aca="false">COUNTIF(I6:I37,"Alta")</f>
         <v>0</v>
       </c>
-      <c r="G41" s="44"/>
+      <c r="G41" s="45"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="39"/>
       <c r="E42" s="39"/>
-      <c r="F42" s="44" t="n">
+      <c r="F42" s="45" t="n">
         <f aca="false">COUNTIF(I6:I37,"Média")</f>
         <v>0</v>
       </c>
-      <c r="G42" s="44"/>
+      <c r="G42" s="45"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
       <c r="E43" s="39"/>
-      <c r="F43" s="44" t="n">
+      <c r="F43" s="45" t="n">
         <f aca="false">COUNTIF(I6:I37,"Baixa")</f>
         <v>0</v>
       </c>
-      <c r="G43" s="44"/>
+      <c r="G43" s="45"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="38" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C45" s="38"/>
       <c r="D45" s="38"/>
@@ -5846,27 +5886,27 @@
       <c r="C46" s="29"/>
       <c r="D46" s="29"/>
       <c r="E46" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G46" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="H46" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="I46" s="44"/>
+      <c r="H46" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="I46" s="45"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="52" t="s">
+      <c r="B47" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
       <c r="E47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="29" t="n">
         <f aca="false">SWOT!E41</f>
@@ -5876,20 +5916,20 @@
         <f aca="false">SWOT!E42</f>
         <v>0</v>
       </c>
-      <c r="H47" s="53" t="n">
+      <c r="H47" s="54" t="n">
         <f aca="false">IF(SUM($G$47:$G$50)=0,0,G47/SUM($G$47:$G$50))</f>
         <v>0</v>
       </c>
-      <c r="I47" s="53"/>
+      <c r="I47" s="54"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="54"/>
-      <c r="D48" s="54"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
       <c r="E48" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="29" t="n">
         <f aca="false">SWOT!H41</f>
@@ -5899,20 +5939,20 @@
         <f aca="false">SWOT!H42</f>
         <v>0</v>
       </c>
-      <c r="H48" s="53" t="n">
+      <c r="H48" s="54" t="n">
         <f aca="false">IF(SUM($G$47:$G$50)=0,0,G48/SUM($G$47:$G$50))</f>
         <v>0</v>
       </c>
-      <c r="I48" s="53"/>
+      <c r="I48" s="54"/>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="55" t="s">
+      <c r="B49" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
       <c r="E49" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F49" s="29" t="n">
         <f aca="false">SWOT!J41</f>
@@ -5922,20 +5962,20 @@
         <f aca="false">SWOT!J42</f>
         <v>0</v>
       </c>
-      <c r="H49" s="53" t="n">
+      <c r="H49" s="54" t="n">
         <f aca="false">IF(SUM($G$47:$G$50)=0,0,G49/SUM($G$47:$G$50))</f>
         <v>0</v>
       </c>
-      <c r="I49" s="53"/>
+      <c r="I49" s="54"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="56" t="s">
+      <c r="B50" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
       <c r="E50" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F50" s="29" t="n">
         <f aca="false">SWOT!K41</f>
@@ -5945,15 +5985,15 @@
         <f aca="false">SWOT!K42</f>
         <v>0</v>
       </c>
-      <c r="H50" s="53" t="n">
+      <c r="H50" s="54" t="n">
         <f aca="false">IF(SUM($G$47:$G$50)=0,0,G50/SUM($G$47:$G$50))</f>
         <v>0</v>
       </c>
-      <c r="I50" s="53"/>
+      <c r="I50" s="54"/>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C52" s="38"/>
       <c r="D52" s="38"/>
@@ -6068,7 +6108,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -6080,7 +6120,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6091,29 +6131,29 @@
       <c r="I2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="57" t="s">
+      <c r="C4" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="D4" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F4" s="57" t="s">
+      <c r="E4" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="F4" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="G4" s="58" t="s">
         <v>180</v>
       </c>
-      <c r="I4" s="57" t="s">
-        <v>154</v>
+      <c r="H4" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6124,22 +6164,22 @@
         <v>101</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>126</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6156,7 +6196,7 @@
         <f aca="false">IF(E6="","",IF(LEFT(E6,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E6,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E6,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G6" s="49" t="str">
+      <c r="G6" s="50" t="str">
         <f aca="false">IF(OR(C6="",E6=""),"",LEFT(C6,1)&amp;LEFT(E6,1)&amp;" — "&amp;IF(LEFT(C6,1)="S",IF(LEFT(E6,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E6,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6177,7 +6217,7 @@
         <f aca="false">IF(E7="","",IF(LEFT(E7,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E7,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E7,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G7" s="49" t="str">
+      <c r="G7" s="50" t="str">
         <f aca="false">IF(OR(C7="",E7=""),"",LEFT(C7,1)&amp;LEFT(E7,1)&amp;" — "&amp;IF(LEFT(C7,1)="S",IF(LEFT(E7,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E7,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6198,7 +6238,7 @@
         <f aca="false">IF(E8="","",IF(LEFT(E8,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E8,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E8,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G8" s="49" t="str">
+      <c r="G8" s="50" t="str">
         <f aca="false">IF(OR(C8="",E8=""),"",LEFT(C8,1)&amp;LEFT(E8,1)&amp;" — "&amp;IF(LEFT(C8,1)="S",IF(LEFT(E8,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E8,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6219,7 +6259,7 @@
         <f aca="false">IF(E9="","",IF(LEFT(E9,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E9,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E9,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G9" s="49" t="str">
+      <c r="G9" s="50" t="str">
         <f aca="false">IF(OR(C9="",E9=""),"",LEFT(C9,1)&amp;LEFT(E9,1)&amp;" — "&amp;IF(LEFT(C9,1)="S",IF(LEFT(E9,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E9,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6240,7 +6280,7 @@
         <f aca="false">IF(E10="","",IF(LEFT(E10,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E10,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E10,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G10" s="49" t="str">
+      <c r="G10" s="50" t="str">
         <f aca="false">IF(OR(C10="",E10=""),"",LEFT(C10,1)&amp;LEFT(E10,1)&amp;" — "&amp;IF(LEFT(C10,1)="S",IF(LEFT(E10,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E10,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6261,7 +6301,7 @@
         <f aca="false">IF(E11="","",IF(LEFT(E11,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E11,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E11,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G11" s="49" t="str">
+      <c r="G11" s="50" t="str">
         <f aca="false">IF(OR(C11="",E11=""),"",LEFT(C11,1)&amp;LEFT(E11,1)&amp;" — "&amp;IF(LEFT(C11,1)="S",IF(LEFT(E11,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E11,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6282,7 +6322,7 @@
         <f aca="false">IF(E12="","",IF(LEFT(E12,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E12,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E12,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G12" s="49" t="str">
+      <c r="G12" s="50" t="str">
         <f aca="false">IF(OR(C12="",E12=""),"",LEFT(C12,1)&amp;LEFT(E12,1)&amp;" — "&amp;IF(LEFT(C12,1)="S",IF(LEFT(E12,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E12,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6303,7 +6343,7 @@
         <f aca="false">IF(E13="","",IF(LEFT(E13,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E13,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E13,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G13" s="49" t="str">
+      <c r="G13" s="50" t="str">
         <f aca="false">IF(OR(C13="",E13=""),"",LEFT(C13,1)&amp;LEFT(E13,1)&amp;" — "&amp;IF(LEFT(C13,1)="S",IF(LEFT(E13,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E13,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6324,7 +6364,7 @@
         <f aca="false">IF(E14="","",IF(LEFT(E14,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E14,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E14,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G14" s="49" t="str">
+      <c r="G14" s="50" t="str">
         <f aca="false">IF(OR(C14="",E14=""),"",LEFT(C14,1)&amp;LEFT(E14,1)&amp;" — "&amp;IF(LEFT(C14,1)="S",IF(LEFT(E14,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E14,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6345,7 +6385,7 @@
         <f aca="false">IF(E15="","",IF(LEFT(E15,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E15,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E15,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G15" s="49" t="str">
+      <c r="G15" s="50" t="str">
         <f aca="false">IF(OR(C15="",E15=""),"",LEFT(C15,1)&amp;LEFT(E15,1)&amp;" — "&amp;IF(LEFT(C15,1)="S",IF(LEFT(E15,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E15,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6366,7 +6406,7 @@
         <f aca="false">IF(E16="","",IF(LEFT(E16,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E16,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E16,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G16" s="49" t="str">
+      <c r="G16" s="50" t="str">
         <f aca="false">IF(OR(C16="",E16=""),"",LEFT(C16,1)&amp;LEFT(E16,1)&amp;" — "&amp;IF(LEFT(C16,1)="S",IF(LEFT(E16,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E16,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6387,7 +6427,7 @@
         <f aca="false">IF(E17="","",IF(LEFT(E17,1)="O",INDEX(SWOT!$C$30:$C$37,VALUE(MID(E17,2,1))),INDEX(SWOT!$I$30:$I$37,VALUE(MID(E17,2,1))))&amp;"")</f>
         <v/>
       </c>
-      <c r="G17" s="49" t="str">
+      <c r="G17" s="50" t="str">
         <f aca="false">IF(OR(C17="",E17=""),"",LEFT(C17,1)&amp;LEFT(E17,1)&amp;" — "&amp;IF(LEFT(C17,1)="S",IF(LEFT(E17,1)="O","Desenvolvimento","Manutenção"),IF(LEFT(E17,1)="O","Crescimento","Sobrevivência")))</f>
         <v/>
       </c>
@@ -6408,7 +6448,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
@@ -6421,7 +6461,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C21" s="39"/>
       <c r="D21" s="39"/>
@@ -6434,7 +6474,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -6447,7 +6487,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -6460,7 +6500,7 @@
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -6473,7 +6513,7 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -6486,26 +6526,26 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
       <c r="E26" s="39"/>
       <c r="F26" s="39"/>
-      <c r="G26" s="42" t="str">
+      <c r="G26" s="43" t="str">
         <f aca="false">IF(SUMPRODUCT((H6:H17&lt;&gt;"")*((C6:C17="")+(E6:E17="")&gt;0))&gt;0,"Há estratégia sem fator","OK")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
-      <c r="G27" s="42" t="str">
+      <c r="G27" s="43" t="str">
         <f aca="false">IF(SUMPRODUCT(((C6:C17&lt;&gt;"")*(D6:D17=""))+((E6:E17&lt;&gt;"")*(F6:F17="")))&gt;0,"Há código sem fator na aba SWOT","OK")</f>
         <v>OK</v>
       </c>
@@ -6602,7 +6642,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6613,29 +6653,29 @@
       <c r="I2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="D4" s="57" t="s">
+      <c r="C4" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="D4" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="E4" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" s="57" t="s">
+      <c r="F4" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="G4" s="58" t="s">
         <v>198</v>
       </c>
-      <c r="I4" s="57" t="s">
+      <c r="H4" s="58" t="s">
         <v>199</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6643,25 +6683,25 @@
         <v>95</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="58" t="n">
+        <v>202</v>
+      </c>
+      <c r="F5" s="59" t="n">
         <v>46356</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6671,10 +6711,10 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="59"/>
+      <c r="F6" s="60"/>
       <c r="G6" s="5"/>
       <c r="H6" s="28"/>
-      <c r="I6" s="49" t="str">
+      <c r="I6" s="50" t="str">
         <f aca="true">IF(D6="","",IF(OR(H6="Concluída",H6="Cancelada"),H6,IF(F6="","Sem prazo",IF(F6&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6686,10 +6726,10 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="59"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="5"/>
       <c r="H7" s="28"/>
-      <c r="I7" s="49" t="str">
+      <c r="I7" s="50" t="str">
         <f aca="true">IF(D7="","",IF(OR(H7="Concluída",H7="Cancelada"),H7,IF(F7="","Sem prazo",IF(F7&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6701,10 +6741,10 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="59"/>
+      <c r="F8" s="60"/>
       <c r="G8" s="5"/>
       <c r="H8" s="28"/>
-      <c r="I8" s="49" t="str">
+      <c r="I8" s="50" t="str">
         <f aca="true">IF(D8="","",IF(OR(H8="Concluída",H8="Cancelada"),H8,IF(F8="","Sem prazo",IF(F8&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6716,10 +6756,10 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="59"/>
+      <c r="F9" s="60"/>
       <c r="G9" s="5"/>
       <c r="H9" s="28"/>
-      <c r="I9" s="49" t="str">
+      <c r="I9" s="50" t="str">
         <f aca="true">IF(D9="","",IF(OR(H9="Concluída",H9="Cancelada"),H9,IF(F9="","Sem prazo",IF(F9&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6731,10 +6771,10 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="59"/>
+      <c r="F10" s="60"/>
       <c r="G10" s="5"/>
       <c r="H10" s="28"/>
-      <c r="I10" s="49" t="str">
+      <c r="I10" s="50" t="str">
         <f aca="true">IF(D10="","",IF(OR(H10="Concluída",H10="Cancelada"),H10,IF(F10="","Sem prazo",IF(F10&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6746,10 +6786,10 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="59"/>
+      <c r="F11" s="60"/>
       <c r="G11" s="5"/>
       <c r="H11" s="28"/>
-      <c r="I11" s="49" t="str">
+      <c r="I11" s="50" t="str">
         <f aca="true">IF(D11="","",IF(OR(H11="Concluída",H11="Cancelada"),H11,IF(F11="","Sem prazo",IF(F11&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6761,10 +6801,10 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="59"/>
+      <c r="F12" s="60"/>
       <c r="G12" s="5"/>
       <c r="H12" s="28"/>
-      <c r="I12" s="49" t="str">
+      <c r="I12" s="50" t="str">
         <f aca="true">IF(D12="","",IF(OR(H12="Concluída",H12="Cancelada"),H12,IF(F12="","Sem prazo",IF(F12&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6776,10 +6816,10 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="59"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
       <c r="H13" s="28"/>
-      <c r="I13" s="49" t="str">
+      <c r="I13" s="50" t="str">
         <f aca="true">IF(D13="","",IF(OR(H13="Concluída",H13="Cancelada"),H13,IF(F13="","Sem prazo",IF(F13&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6791,10 +6831,10 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="59"/>
+      <c r="F14" s="60"/>
       <c r="G14" s="5"/>
       <c r="H14" s="28"/>
-      <c r="I14" s="49" t="str">
+      <c r="I14" s="50" t="str">
         <f aca="true">IF(D14="","",IF(OR(H14="Concluída",H14="Cancelada"),H14,IF(F14="","Sem prazo",IF(F14&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6806,10 +6846,10 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="59"/>
+      <c r="F15" s="60"/>
       <c r="G15" s="5"/>
       <c r="H15" s="28"/>
-      <c r="I15" s="49" t="str">
+      <c r="I15" s="50" t="str">
         <f aca="true">IF(D15="","",IF(OR(H15="Concluída",H15="Cancelada"),H15,IF(F15="","Sem prazo",IF(F15&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6821,10 +6861,10 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="59"/>
+      <c r="F16" s="60"/>
       <c r="G16" s="5"/>
       <c r="H16" s="28"/>
-      <c r="I16" s="49" t="str">
+      <c r="I16" s="50" t="str">
         <f aca="true">IF(D16="","",IF(OR(H16="Concluída",H16="Cancelada"),H16,IF(F16="","Sem prazo",IF(F16&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6836,10 +6876,10 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="59"/>
+      <c r="F17" s="60"/>
       <c r="G17" s="5"/>
       <c r="H17" s="28"/>
-      <c r="I17" s="49" t="str">
+      <c r="I17" s="50" t="str">
         <f aca="true">IF(D17="","",IF(OR(H17="Concluída",H17="Cancelada"),H17,IF(F17="","Sem prazo",IF(F17&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6851,10 +6891,10 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="59"/>
+      <c r="F18" s="60"/>
       <c r="G18" s="5"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="49" t="str">
+      <c r="I18" s="50" t="str">
         <f aca="true">IF(D18="","",IF(OR(H18="Concluída",H18="Cancelada"),H18,IF(F18="","Sem prazo",IF(F18&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6866,10 +6906,10 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="59"/>
+      <c r="F19" s="60"/>
       <c r="G19" s="5"/>
       <c r="H19" s="28"/>
-      <c r="I19" s="49" t="str">
+      <c r="I19" s="50" t="str">
         <f aca="true">IF(D19="","",IF(OR(H19="Concluída",H19="Cancelada"),H19,IF(F19="","Sem prazo",IF(F19&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6881,10 +6921,10 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="59"/>
+      <c r="F20" s="60"/>
       <c r="G20" s="5"/>
       <c r="H20" s="28"/>
-      <c r="I20" s="49" t="str">
+      <c r="I20" s="50" t="str">
         <f aca="true">IF(D20="","",IF(OR(H20="Concluída",H20="Cancelada"),H20,IF(F20="","Sem prazo",IF(F20&lt;TODAY(),"Atrasada","No prazo"))))</f>
         <v/>
       </c>
@@ -6903,7 +6943,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -6916,7 +6956,7 @@
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C24" s="39"/>
       <c r="D24" s="39"/>
@@ -6929,7 +6969,7 @@
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -6942,7 +6982,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
@@ -6955,7 +6995,7 @@
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C27" s="39"/>
       <c r="D27" s="39"/>
@@ -6968,7 +7008,7 @@
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" s="39"/>
       <c r="D28" s="39"/>
@@ -6981,13 +7021,13 @@
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="39"/>
       <c r="F29" s="39"/>
-      <c r="G29" s="53" t="n">
+      <c r="G29" s="54" t="n">
         <f aca="false">IF(G23=0,0,G24/G23)</f>
         <v>0</v>
       </c>
@@ -7031,12 +7071,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H6:H20" type="list">
+      <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F6:F20" type="date">
       <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H6:H20" type="list">
-      <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7069,7 +7109,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -7077,24 +7117,24 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" s="57" t="s">
+      <c r="C4" s="58" t="s">
         <v>214</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7102,7 +7142,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D5" s="28"/>
       <c r="E5" s="5"/>
@@ -7112,7 +7152,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="5"/>
@@ -7122,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="5"/>
@@ -7132,7 +7172,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D8" s="28"/>
       <c r="E8" s="5"/>
@@ -7142,7 +7182,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="5"/>
@@ -7152,7 +7192,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="5"/>
@@ -7162,7 +7202,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D11" s="28"/>
       <c r="E11" s="5"/>
@@ -7172,7 +7212,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="5"/>
@@ -7182,7 +7222,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="5"/>
@@ -7192,7 +7232,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D14" s="28"/>
       <c r="E14" s="5"/>
@@ -7202,7 +7242,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D15" s="28"/>
       <c r="E15" s="5"/>
@@ -7212,7 +7252,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="5"/>
@@ -7227,7 +7267,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" s="39"/>
       <c r="D19" s="29" t="n">
@@ -7237,7 +7277,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="39"/>
       <c r="D20" s="29" t="n">
@@ -7247,7 +7287,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="39"/>
       <c r="D21" s="29" t="n">
@@ -7257,7 +7297,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="39" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C22" s="39"/>
       <c r="D22" s="29" t="n">
@@ -7267,17 +7307,17 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="39" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="39"/>
-      <c r="D23" s="53" t="n">
+      <c r="D23" s="54" t="n">
         <f aca="false">D19/ROWS(D5:D16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C24" s="39"/>
       <c r="D24" s="29" t="str">
@@ -7330,7 +7370,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:M56"/>
+  <dimension ref="B1:M57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -7365,7 +7405,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -7384,124 +7424,124 @@
         <v>78</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="60" t="s">
-        <v>233</v>
-      </c>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
+      <c r="D4" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="4" t="s">
         <v>79</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="60" t="s">
-        <v>201</v>
-      </c>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
+      <c r="J4" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="60" t="s">
-        <v>234</v>
-      </c>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="D5" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
       <c r="H5" s="4" t="s">
         <v>81</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="61" t="n">
+      <c r="J5" s="62" t="n">
         <v>46294</v>
       </c>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="60" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
+      <c r="D6" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
       <c r="H6" s="4" t="s">
         <v>83</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="60" t="s">
-        <v>236</v>
-      </c>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
+      <c r="J6" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="60" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
+      <c r="D7" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
+      <c r="D8" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
       <c r="H8" s="4" t="s">
         <v>86</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="J8" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
+      <c r="D9" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
@@ -7593,7 +7633,7 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="26"/>
@@ -7612,13 +7652,13 @@
         <v>98</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D16" s="9"/>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="62" t="n">
+      <c r="F16" s="63" t="n">
         <v>4</v>
       </c>
       <c r="G16" s="29" t="n">
@@ -7632,10 +7672,10 @@
         <v>97</v>
       </c>
       <c r="J16" s="11"/>
-      <c r="K16" s="63" t="n">
+      <c r="K16" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="L16" s="63" t="n">
+      <c r="L16" s="64" t="n">
         <v>4</v>
       </c>
       <c r="M16" s="29" t="n">
@@ -7648,13 +7688,13 @@
         <v>100</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D17" s="9"/>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="F17" s="62" t="n">
+      <c r="F17" s="63" t="n">
         <v>4</v>
       </c>
       <c r="G17" s="29" t="n">
@@ -7665,13 +7705,13 @@
         <v>101</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J17" s="11"/>
-      <c r="K17" s="63" t="n">
+      <c r="K17" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="L17" s="63" t="n">
+      <c r="L17" s="64" t="n">
         <v>5</v>
       </c>
       <c r="M17" s="29" t="n">
@@ -7684,13 +7724,13 @@
         <v>102</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D18" s="9"/>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="62" t="n">
+      <c r="F18" s="63" t="n">
         <v>3</v>
       </c>
       <c r="G18" s="29" t="n">
@@ -7701,13 +7741,13 @@
         <v>103</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J18" s="11"/>
-      <c r="K18" s="63" t="n">
+      <c r="K18" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="L18" s="63" t="n">
+      <c r="L18" s="64" t="n">
         <v>3</v>
       </c>
       <c r="M18" s="29" t="n">
@@ -7720,13 +7760,13 @@
         <v>104</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D19" s="9"/>
-      <c r="E19" s="62" t="n">
+      <c r="E19" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="62" t="n">
+      <c r="F19" s="63" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="29" t="n">
@@ -7737,13 +7777,13 @@
         <v>105</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J19" s="11"/>
-      <c r="K19" s="63" t="n">
+      <c r="K19" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="L19" s="63" t="n">
+      <c r="L19" s="64" t="n">
         <v>3</v>
       </c>
       <c r="M19" s="29" t="n">
@@ -7755,10 +7795,10 @@
       <c r="B20" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
       <c r="G20" s="29" t="str">
         <f aca="false">IF(OR(E20="",F20=""),"",E20*F20)</f>
         <v/>
@@ -7766,10 +7806,10 @@
       <c r="H20" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
       <c r="M20" s="29" t="str">
         <f aca="false">IF(OR(K20="",L20=""),"",K20*L20)</f>
         <v/>
@@ -7779,10 +7819,10 @@
       <c r="B21" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
       <c r="G21" s="29" t="str">
         <f aca="false">IF(OR(E21="",F21=""),"",E21*F21)</f>
         <v/>
@@ -7790,10 +7830,10 @@
       <c r="H21" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
       <c r="M21" s="29" t="str">
         <f aca="false">IF(OR(K21="",L21=""),"",K21*L21)</f>
         <v/>
@@ -7803,10 +7843,10 @@
       <c r="B22" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
       <c r="G22" s="29" t="str">
         <f aca="false">IF(OR(E22="",F22=""),"",E22*F22)</f>
         <v/>
@@ -7814,10 +7854,10 @@
       <c r="H22" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
       <c r="M22" s="29" t="str">
         <f aca="false">IF(OR(K22="",L22=""),"",K22*L22)</f>
         <v/>
@@ -7827,10 +7867,10 @@
       <c r="B23" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
       <c r="G23" s="29" t="str">
         <f aca="false">IF(OR(E23="",F23=""),"",E23*F23)</f>
         <v/>
@@ -7838,10 +7878,10 @@
       <c r="H23" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
       <c r="M23" s="29" t="str">
         <f aca="false">IF(OR(K23="",L23=""),"",K23*L23)</f>
         <v/>
@@ -7937,7 +7977,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -7959,10 +7999,10 @@
         <v>118</v>
       </c>
       <c r="D30" s="13"/>
-      <c r="E30" s="65" t="n">
+      <c r="E30" s="66" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="65" t="n">
+      <c r="F30" s="66" t="n">
         <v>4</v>
       </c>
       <c r="G30" s="29" t="n">
@@ -7976,10 +8016,10 @@
         <v>119</v>
       </c>
       <c r="J30" s="15"/>
-      <c r="K30" s="66" t="n">
+      <c r="K30" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="L30" s="66" t="n">
+      <c r="L30" s="67" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="29" t="n">
@@ -7992,13 +8032,13 @@
         <v>122</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D31" s="13"/>
-      <c r="E31" s="65" t="n">
+      <c r="E31" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="65" t="n">
+      <c r="F31" s="66" t="n">
         <v>3</v>
       </c>
       <c r="G31" s="29" t="n">
@@ -8009,13 +8049,13 @@
         <v>123</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J31" s="15"/>
-      <c r="K31" s="66" t="n">
+      <c r="K31" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="L31" s="66" t="n">
+      <c r="L31" s="67" t="n">
         <v>3</v>
       </c>
       <c r="M31" s="29" t="n">
@@ -8028,13 +8068,13 @@
         <v>124</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D32" s="13"/>
-      <c r="E32" s="65" t="n">
+      <c r="E32" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="65" t="n">
+      <c r="F32" s="66" t="n">
         <v>3</v>
       </c>
       <c r="G32" s="29" t="n">
@@ -8045,13 +8085,13 @@
         <v>125</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J32" s="15"/>
-      <c r="K32" s="66" t="n">
+      <c r="K32" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="66" t="n">
+      <c r="L32" s="67" t="n">
         <v>4</v>
       </c>
       <c r="M32" s="29" t="n">
@@ -8064,13 +8104,13 @@
         <v>126</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D33" s="13"/>
-      <c r="E33" s="65" t="n">
+      <c r="E33" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="F33" s="65" t="n">
+      <c r="F33" s="66" t="n">
         <v>4</v>
       </c>
       <c r="G33" s="29" t="n">
@@ -8081,13 +8121,13 @@
         <v>127</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J33" s="15"/>
-      <c r="K33" s="66" t="n">
+      <c r="K33" s="67" t="n">
         <v>2</v>
       </c>
-      <c r="L33" s="66" t="n">
+      <c r="L33" s="67" t="n">
         <v>2</v>
       </c>
       <c r="M33" s="29" t="n">
@@ -8099,10 +8139,10 @@
       <c r="B34" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
       <c r="G34" s="29" t="str">
         <f aca="false">IF(OR(E34="",F34=""),"",E34*F34)</f>
         <v/>
@@ -8110,10 +8150,10 @@
       <c r="H34" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
       <c r="M34" s="29" t="str">
         <f aca="false">IF(OR(K34="",L34=""),"",K34*L34)</f>
         <v/>
@@ -8123,10 +8163,10 @@
       <c r="B35" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
       <c r="G35" s="29" t="str">
         <f aca="false">IF(OR(E35="",F35=""),"",E35*F35)</f>
         <v/>
@@ -8134,10 +8174,10 @@
       <c r="H35" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="I35" s="60"/>
-      <c r="J35" s="60"/>
-      <c r="K35" s="64"/>
-      <c r="L35" s="64"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
       <c r="M35" s="29" t="str">
         <f aca="false">IF(OR(K35="",L35=""),"",K35*L35)</f>
         <v/>
@@ -8147,10 +8187,10 @@
       <c r="B36" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
       <c r="G36" s="29" t="str">
         <f aca="false">IF(OR(E36="",F36=""),"",E36*F36)</f>
         <v/>
@@ -8158,10 +8198,10 @@
       <c r="H36" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="I36" s="60"/>
-      <c r="J36" s="60"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
       <c r="M36" s="29" t="str">
         <f aca="false">IF(OR(K36="",L36=""),"",K36*L36)</f>
         <v/>
@@ -8171,10 +8211,10 @@
       <c r="B37" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
       <c r="G37" s="29" t="str">
         <f aca="false">IF(OR(E37="",F37=""),"",E37*F37)</f>
         <v/>
@@ -8182,10 +8222,10 @@
       <c r="H37" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
       <c r="M37" s="29" t="str">
         <f aca="false">IF(OR(K37="",L37=""),"",K37*L37)</f>
         <v/>
@@ -8287,50 +8327,59 @@
       <c r="L42" s="41"/>
       <c r="M42" s="41"/>
     </row>
-    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="39" t="s">
         <v>143</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
-      <c r="E43" s="42" t="str">
+      <c r="E43" s="42" t="n">
+        <f aca="false">IF(COUNT(G16:G23)=0,"",AVERAGE(G16:G23))</f>
+        <v>14.25</v>
+      </c>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42" t="n">
+        <f aca="false">IF(COUNT(M16:M23)=0,"",AVERAGE(M16:M23))</f>
+        <v>13.75</v>
+      </c>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42" t="n">
+        <f aca="false">IF(COUNT(G30:G37)=0,"",AVERAGE(G30:G37))</f>
+        <v>12.75</v>
+      </c>
+      <c r="K43" s="42" t="n">
+        <f aca="false">IF(COUNT(M30:M37)=0,"",AVERAGE(M30:M37))</f>
+        <v>11</v>
+      </c>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="43" t="str">
         <f aca="false">IF(E41=0,"Liste os fatores",IF(E41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(G16:G23)&lt;E41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42" t="str">
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43" t="str">
         <f aca="false">IF(H41=0,"Liste os fatores",IF(H41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(M16:M23)&lt;H41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42" t="str">
+      <c r="I44" s="43"/>
+      <c r="J44" s="43" t="str">
         <f aca="false">IF(J41=0,"Liste os fatores",IF(J41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(G30:G37)&lt;J41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="K43" s="42" t="str">
+      <c r="K44" s="43" t="str">
         <f aca="false">IF(K41=0,"Liste os fatores",IF(K41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(M30:M37)&lt;K41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="L43" s="42"/>
-      <c r="M43" s="42"/>
-    </row>
-    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="43" t="n">
-        <f aca="false">E42-H42</f>
-        <v>2</v>
-      </c>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
       <c r="L44" s="43"/>
       <c r="M44" s="43"/>
     </row>
@@ -8343,17 +8392,17 @@
       <c r="E45" s="39"/>
       <c r="F45" s="39"/>
       <c r="G45" s="39"/>
-      <c r="H45" s="43" t="n">
-        <f aca="false">J42-K42</f>
-        <v>7</v>
-      </c>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-    </row>
-    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H45" s="44" t="n">
+        <f aca="false">IF(OR(E43="",H43=""),"",E43-H43)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
+      <c r="M45" s="44"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="39" t="s">
         <v>146</v>
       </c>
@@ -8362,9 +8411,9 @@
       <c r="E46" s="39"/>
       <c r="F46" s="39"/>
       <c r="G46" s="39"/>
-      <c r="H46" s="44" t="str">
-        <f aca="false">IF(OR(COUNT(G16:G23)=0,COUNT(M16:M23)=0,COUNT(G30:G37)=0,COUNT(M30:M37)=0),"Dê notas aos quatro quadrantes para ver a postura",IF(E42&gt;=H42,IF(J42&gt;=K42,"Desenvolvimento: usar as forças para aproveitar as oportunidades","Manutenção: usar as forças para enfrentar as ameaças"),IF(J42&gt;=K42,"Crescimento: corrigir as fraquezas para aproveitar as oportunidades","Sobrevivência: reduzir as fraquezas e proteger-se das ameaças")))</f>
-        <v>Desenvolvimento: usar as forças para aproveitar as oportunidades</v>
+      <c r="H46" s="44" t="n">
+        <f aca="false">IF(OR(J43="",K43=""),"",J43-K43)</f>
+        <v>1.75</v>
       </c>
       <c r="I46" s="44"/>
       <c r="J46" s="44"/>
@@ -8372,7 +8421,7 @@
       <c r="L46" s="44"/>
       <c r="M46" s="44"/>
     </row>
-    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="39" t="s">
         <v>147</v>
       </c>
@@ -8381,9 +8430,9 @@
       <c r="E47" s="39"/>
       <c r="F47" s="39"/>
       <c r="G47" s="39"/>
-      <c r="H47" s="45" t="n">
-        <f aca="false">COUNTA(D4,J4,D5,J5,D6,J6,D7,D8,J8,D9)</f>
-        <v>10</v>
+      <c r="H47" s="45" t="str">
+        <f aca="false">IF(OR(COUNT(G16:G23)=0,COUNT(M16:M23)=0,COUNT(G30:G37)=0,COUNT(M30:M37)=0),"Dê notas aos quatro quadrantes para ver a postura",IF(E43&gt;=H43,IF(J43&gt;=K43,"Desenvolvimento: usar as forças para aproveitar as oportunidades","Manutenção: usar as forças para enfrentar as ameaças"),IF(J43&gt;=K43,"Crescimento: corrigir as fraquezas para aproveitar as oportunidades","Sobrevivência: reduzir as fraquezas e proteger-se das ameaças")))</f>
+        <v>Desenvolvimento: usar as forças para aproveitar as oportunidades</v>
       </c>
       <c r="I47" s="45"/>
       <c r="J47" s="45"/>
@@ -8391,72 +8440,71 @@
       <c r="L47" s="45"/>
       <c r="M47" s="45"/>
     </row>
-    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="46" t="n">
+        <f aca="false">COUNTA(D4,J4,D5,J5,D6,J6,D7,D8,J8,D9)</f>
+        <v>10</v>
+      </c>
+      <c r="I48" s="46"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="46"/>
+      <c r="L48" s="46"/>
+      <c r="M48" s="46"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="C50" s="44"/>
-      <c r="D50" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E50" s="29" t="s">
+      <c r="B50" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="38"/>
+    </row>
+    <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-    </row>
-    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="67" t="s">
-        <v>187</v>
-      </c>
-      <c r="C51" s="67"/>
-      <c r="D51" s="68" t="s">
-        <v>255</v>
-      </c>
-      <c r="E51" s="7" t="s">
+      <c r="C51" s="45"/>
+      <c r="D51" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+    </row>
+    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="68"/>
+      <c r="D52" s="69" t="s">
         <v>256</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-    </row>
-    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="67" t="s">
-        <v>187</v>
-      </c>
-      <c r="C52" s="67"/>
-      <c r="D52" s="68" t="s">
+      <c r="E52" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>258</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -8468,15 +8516,15 @@
       <c r="M52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53" s="67"/>
-      <c r="D53" s="68" t="s">
+      <c r="B53" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" s="68"/>
+      <c r="D53" s="69" t="s">
+        <v>258</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>260</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -8488,15 +8536,15 @@
       <c r="M53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="C54" s="67"/>
-      <c r="D54" s="68" t="s">
+      <c r="B54" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" s="68"/>
+      <c r="D54" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>261</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>262</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
@@ -8508,15 +8556,15 @@
       <c r="M54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="C55" s="67"/>
-      <c r="D55" s="68" t="s">
+      <c r="B55" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="68"/>
+      <c r="D55" s="69" t="s">
+        <v>262</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>264</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -8528,15 +8576,15 @@
       <c r="M55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="67" t="s">
+      <c r="B56" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="C56" s="67"/>
-      <c r="D56" s="68" t="s">
+      <c r="C56" s="68"/>
+      <c r="D56" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>266</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
@@ -8547,8 +8595,28 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
+    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="C57" s="68"/>
+      <c r="D57" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="116">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:C4"/>
@@ -8638,17 +8706,19 @@
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="K43:M43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="K44:M44"/>
     <mergeCell ref="B45:G45"/>
     <mergeCell ref="H45:M45"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="H46:M46"/>
     <mergeCell ref="B47:G47"/>
     <mergeCell ref="H47:M47"/>
-    <mergeCell ref="B49:M49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="E50:M50"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="B50:M50"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="E51:M51"/>
     <mergeCell ref="B52:C52"/>
@@ -8661,8 +8731,10 @@
     <mergeCell ref="E55:M55"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="E56:M56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="E57:M57"/>
   </mergeCells>
-  <conditionalFormatting sqref="E43:M43">
+  <conditionalFormatting sqref="E44:M44">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -8696,7 +8768,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:M55"/>
+  <dimension ref="B1:M56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -8731,7 +8803,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -8750,124 +8822,124 @@
         <v>78</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="60" t="s">
-        <v>267</v>
-      </c>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
+      <c r="D4" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="4" t="s">
         <v>79</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="60" t="s">
-        <v>268</v>
-      </c>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
+      <c r="J4" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="60" t="s">
-        <v>269</v>
-      </c>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="D5" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
       <c r="H5" s="4" t="s">
         <v>81</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="61" t="n">
-        <v>46294</v>
-      </c>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
+      <c r="J5" s="62" t="n">
+        <v>46164</v>
+      </c>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
+      <c r="D6" s="61" t="s">
+        <v>271</v>
+      </c>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
       <c r="H6" s="4" t="s">
         <v>83</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="60" t="s">
-        <v>236</v>
-      </c>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
+      <c r="J6" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="60" t="s">
-        <v>271</v>
-      </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
+      <c r="D7" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
+      <c r="D8" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
       <c r="H8" s="4" t="s">
         <v>86</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="60" t="s">
-        <v>272</v>
-      </c>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="J8" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="60" t="s">
-        <v>273</v>
-      </c>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
+      <c r="D9" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="61"/>
+      <c r="M9" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
@@ -8959,7 +9031,7 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="26"/>
@@ -8978,13 +9050,13 @@
         <v>98</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D16" s="9"/>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="62" t="n">
+      <c r="F16" s="63" t="n">
         <v>4</v>
       </c>
       <c r="G16" s="29" t="n">
@@ -8995,13 +9067,13 @@
         <v>99</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J16" s="11"/>
-      <c r="K16" s="63" t="n">
+      <c r="K16" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="L16" s="63" t="n">
+      <c r="L16" s="64" t="n">
         <v>4</v>
       </c>
       <c r="M16" s="29" t="n">
@@ -9014,13 +9086,13 @@
         <v>100</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D17" s="9"/>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="F17" s="62" t="n">
+      <c r="F17" s="63" t="n">
         <v>4</v>
       </c>
       <c r="G17" s="29" t="n">
@@ -9031,13 +9103,13 @@
         <v>101</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J17" s="11"/>
-      <c r="K17" s="63" t="n">
+      <c r="K17" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="L17" s="63" t="n">
+      <c r="L17" s="64" t="n">
         <v>4</v>
       </c>
       <c r="M17" s="29" t="n">
@@ -9050,13 +9122,13 @@
         <v>102</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D18" s="9"/>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="62" t="n">
+      <c r="F18" s="63" t="n">
         <v>3</v>
       </c>
       <c r="G18" s="29" t="n">
@@ -9067,13 +9139,13 @@
         <v>103</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J18" s="11"/>
-      <c r="K18" s="63" t="n">
+      <c r="K18" s="64" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="63" t="n">
+      <c r="L18" s="64" t="n">
         <v>4</v>
       </c>
       <c r="M18" s="29" t="n">
@@ -9085,10 +9157,10 @@
       <c r="B19" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
       <c r="G19" s="29" t="str">
         <f aca="false">IF(OR(E19="",F19=""),"",E19*F19)</f>
         <v/>
@@ -9097,13 +9169,13 @@
         <v>105</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J19" s="11"/>
-      <c r="K19" s="63" t="n">
+      <c r="K19" s="64" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="63" t="n">
+      <c r="L19" s="64" t="n">
         <v>3</v>
       </c>
       <c r="M19" s="29" t="n">
@@ -9115,10 +9187,10 @@
       <c r="B20" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
       <c r="G20" s="29" t="str">
         <f aca="false">IF(OR(E20="",F20=""),"",E20*F20)</f>
         <v/>
@@ -9126,10 +9198,10 @@
       <c r="H20" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
       <c r="M20" s="29" t="str">
         <f aca="false">IF(OR(K20="",L20=""),"",K20*L20)</f>
         <v/>
@@ -9139,10 +9211,10 @@
       <c r="B21" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
       <c r="G21" s="29" t="str">
         <f aca="false">IF(OR(E21="",F21=""),"",E21*F21)</f>
         <v/>
@@ -9150,10 +9222,10 @@
       <c r="H21" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
       <c r="M21" s="29" t="str">
         <f aca="false">IF(OR(K21="",L21=""),"",K21*L21)</f>
         <v/>
@@ -9163,10 +9235,10 @@
       <c r="B22" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
       <c r="G22" s="29" t="str">
         <f aca="false">IF(OR(E22="",F22=""),"",E22*F22)</f>
         <v/>
@@ -9174,10 +9246,10 @@
       <c r="H22" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
       <c r="M22" s="29" t="str">
         <f aca="false">IF(OR(K22="",L22=""),"",K22*L22)</f>
         <v/>
@@ -9187,10 +9259,10 @@
       <c r="B23" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
       <c r="G23" s="29" t="str">
         <f aca="false">IF(OR(E23="",F23=""),"",E23*F23)</f>
         <v/>
@@ -9198,10 +9270,10 @@
       <c r="H23" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
       <c r="M23" s="29" t="str">
         <f aca="false">IF(OR(K23="",L23=""),"",K23*L23)</f>
         <v/>
@@ -9297,7 +9369,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -9316,13 +9388,13 @@
         <v>120</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D30" s="13"/>
-      <c r="E30" s="65" t="n">
+      <c r="E30" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="65" t="n">
+      <c r="F30" s="66" t="n">
         <v>3</v>
       </c>
       <c r="G30" s="29" t="n">
@@ -9333,13 +9405,13 @@
         <v>121</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J30" s="15"/>
-      <c r="K30" s="66" t="n">
+      <c r="K30" s="67" t="n">
         <v>5</v>
       </c>
-      <c r="L30" s="66" t="n">
+      <c r="L30" s="67" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="29" t="n">
@@ -9352,13 +9424,13 @@
         <v>122</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D31" s="13"/>
-      <c r="E31" s="65" t="n">
+      <c r="E31" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="65" t="n">
+      <c r="F31" s="66" t="n">
         <v>4</v>
       </c>
       <c r="G31" s="29" t="n">
@@ -9369,13 +9441,13 @@
         <v>123</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J31" s="15"/>
-      <c r="K31" s="66" t="n">
+      <c r="K31" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="L31" s="66" t="n">
+      <c r="L31" s="67" t="n">
         <v>3</v>
       </c>
       <c r="M31" s="29" t="n">
@@ -9388,13 +9460,13 @@
         <v>124</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D32" s="13"/>
-      <c r="E32" s="65" t="n">
+      <c r="E32" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="65" t="n">
+      <c r="F32" s="66" t="n">
         <v>3</v>
       </c>
       <c r="G32" s="29" t="n">
@@ -9405,13 +9477,13 @@
         <v>125</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J32" s="15"/>
-      <c r="K32" s="66" t="n">
+      <c r="K32" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="66" t="n">
+      <c r="L32" s="67" t="n">
         <v>3</v>
       </c>
       <c r="M32" s="29" t="n">
@@ -9423,10 +9495,10 @@
       <c r="B33" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
       <c r="G33" s="29" t="str">
         <f aca="false">IF(OR(E33="",F33=""),"",E33*F33)</f>
         <v/>
@@ -9435,13 +9507,13 @@
         <v>127</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J33" s="15"/>
-      <c r="K33" s="66" t="n">
+      <c r="K33" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="L33" s="66" t="n">
+      <c r="L33" s="67" t="n">
         <v>4</v>
       </c>
       <c r="M33" s="29" t="n">
@@ -9453,10 +9525,10 @@
       <c r="B34" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
       <c r="G34" s="29" t="str">
         <f aca="false">IF(OR(E34="",F34=""),"",E34*F34)</f>
         <v/>
@@ -9464,10 +9536,10 @@
       <c r="H34" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
       <c r="M34" s="29" t="str">
         <f aca="false">IF(OR(K34="",L34=""),"",K34*L34)</f>
         <v/>
@@ -9477,10 +9549,10 @@
       <c r="B35" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
       <c r="G35" s="29" t="str">
         <f aca="false">IF(OR(E35="",F35=""),"",E35*F35)</f>
         <v/>
@@ -9488,10 +9560,10 @@
       <c r="H35" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="I35" s="60"/>
-      <c r="J35" s="60"/>
-      <c r="K35" s="64"/>
-      <c r="L35" s="64"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
       <c r="M35" s="29" t="str">
         <f aca="false">IF(OR(K35="",L35=""),"",K35*L35)</f>
         <v/>
@@ -9501,10 +9573,10 @@
       <c r="B36" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
       <c r="G36" s="29" t="str">
         <f aca="false">IF(OR(E36="",F36=""),"",E36*F36)</f>
         <v/>
@@ -9512,10 +9584,10 @@
       <c r="H36" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="I36" s="60"/>
-      <c r="J36" s="60"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
       <c r="M36" s="29" t="str">
         <f aca="false">IF(OR(K36="",L36=""),"",K36*L36)</f>
         <v/>
@@ -9525,10 +9597,10 @@
       <c r="B37" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
       <c r="G37" s="29" t="str">
         <f aca="false">IF(OR(E37="",F37=""),"",E37*F37)</f>
         <v/>
@@ -9536,10 +9608,10 @@
       <c r="H37" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="60"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
       <c r="M37" s="29" t="str">
         <f aca="false">IF(OR(K37="",L37=""),"",K37*L37)</f>
         <v/>
@@ -9641,50 +9713,59 @@
       <c r="L42" s="41"/>
       <c r="M42" s="41"/>
     </row>
-    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="39" t="s">
         <v>143</v>
       </c>
       <c r="C43" s="39"/>
       <c r="D43" s="39"/>
-      <c r="E43" s="42" t="str">
+      <c r="E43" s="42" t="n">
+        <f aca="false">IF(COUNT(G16:G23)=0,"",AVERAGE(G16:G23))</f>
+        <v>15.6666666666667</v>
+      </c>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42" t="n">
+        <f aca="false">IF(COUNT(M16:M23)=0,"",AVERAGE(M16:M23))</f>
+        <v>15.25</v>
+      </c>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42" t="n">
+        <f aca="false">IF(COUNT(G30:G37)=0,"",AVERAGE(G30:G37))</f>
+        <v>12.3333333333333</v>
+      </c>
+      <c r="K43" s="42" t="n">
+        <f aca="false">IF(COUNT(M30:M37)=0,"",AVERAGE(M30:M37))</f>
+        <v>14.25</v>
+      </c>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="43" t="str">
         <f aca="false">IF(E41=0,"Liste os fatores",IF(E41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(G16:G23)&lt;E41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42" t="str">
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43" t="str">
         <f aca="false">IF(H41=0,"Liste os fatores",IF(H41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(M16:M23)&lt;H41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42" t="str">
+      <c r="I44" s="43"/>
+      <c r="J44" s="43" t="str">
         <f aca="false">IF(J41=0,"Liste os fatores",IF(J41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(G30:G37)&lt;J41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="K43" s="42" t="str">
+      <c r="K44" s="43" t="str">
         <f aca="false">IF(K41=0,"Liste os fatores",IF(K41&lt;3,"Poucos fatores: liste ao menos 3",IF(COUNT(M30:M37)&lt;K41,"Há fator sem nota","OK")))</f>
         <v>OK</v>
       </c>
-      <c r="L43" s="42"/>
-      <c r="M43" s="42"/>
-    </row>
-    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="43" t="n">
-        <f aca="false">E42-H42</f>
-        <v>-14</v>
-      </c>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
       <c r="L44" s="43"/>
       <c r="M44" s="43"/>
     </row>
@@ -9697,17 +9778,17 @@
       <c r="E45" s="39"/>
       <c r="F45" s="39"/>
       <c r="G45" s="39"/>
-      <c r="H45" s="43" t="n">
-        <f aca="false">J42-K42</f>
-        <v>-20</v>
-      </c>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-    </row>
-    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H45" s="44" t="n">
+        <f aca="false">IF(OR(E43="",H43=""),"",E43-H43)</f>
+        <v>0.416666666666666</v>
+      </c>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
+      <c r="M45" s="44"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="39" t="s">
         <v>146</v>
       </c>
@@ -9716,9 +9797,9 @@
       <c r="E46" s="39"/>
       <c r="F46" s="39"/>
       <c r="G46" s="39"/>
-      <c r="H46" s="44" t="str">
-        <f aca="false">IF(OR(COUNT(G16:G23)=0,COUNT(M16:M23)=0,COUNT(G30:G37)=0,COUNT(M30:M37)=0),"Dê notas aos quatro quadrantes para ver a postura",IF(E42&gt;=H42,IF(J42&gt;=K42,"Desenvolvimento: usar as forças para aproveitar as oportunidades","Manutenção: usar as forças para enfrentar as ameaças"),IF(J42&gt;=K42,"Crescimento: corrigir as fraquezas para aproveitar as oportunidades","Sobrevivência: reduzir as fraquezas e proteger-se das ameaças")))</f>
-        <v>Sobrevivência: reduzir as fraquezas e proteger-se das ameaças</v>
+      <c r="H46" s="44" t="n">
+        <f aca="false">IF(OR(J43="",K43=""),"",J43-K43)</f>
+        <v>-1.91666666666667</v>
       </c>
       <c r="I46" s="44"/>
       <c r="J46" s="44"/>
@@ -9726,7 +9807,7 @@
       <c r="L46" s="44"/>
       <c r="M46" s="44"/>
     </row>
-    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="39" t="s">
         <v>147</v>
       </c>
@@ -9735,9 +9816,9 @@
       <c r="E47" s="39"/>
       <c r="F47" s="39"/>
       <c r="G47" s="39"/>
-      <c r="H47" s="45" t="n">
-        <f aca="false">COUNTA(D4,J4,D5,J5,D6,J6,D7,D8,J8,D9)</f>
-        <v>10</v>
+      <c r="H47" s="45" t="str">
+        <f aca="false">IF(OR(COUNT(G16:G23)=0,COUNT(M16:M23)=0,COUNT(G30:G37)=0,COUNT(M30:M37)=0),"Dê notas aos quatro quadrantes para ver a postura",IF(E43&gt;=H43,IF(J43&gt;=K43,"Desenvolvimento: usar as forças para aproveitar as oportunidades","Manutenção: usar as forças para enfrentar as ameaças"),IF(J43&gt;=K43,"Crescimento: corrigir as fraquezas para aproveitar as oportunidades","Sobrevivência: reduzir as fraquezas e proteger-se das ameaças")))</f>
+        <v>Manutenção: usar as forças para enfrentar as ameaças</v>
       </c>
       <c r="I47" s="45"/>
       <c r="J47" s="45"/>
@@ -9745,72 +9826,71 @@
       <c r="L47" s="45"/>
       <c r="M47" s="45"/>
     </row>
-    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="46" t="n">
+        <f aca="false">COUNTA(D4,J4,D5,J5,D6,J6,D7,D8,J8,D9)</f>
+        <v>10</v>
+      </c>
+      <c r="I48" s="46"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="46"/>
+      <c r="L48" s="46"/>
+      <c r="M48" s="46"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="C50" s="44"/>
-      <c r="D50" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E50" s="29" t="s">
+      <c r="B50" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="38"/>
+    </row>
+    <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-    </row>
-    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="C51" s="67"/>
-      <c r="D51" s="68" t="s">
-        <v>288</v>
-      </c>
-      <c r="E51" s="7" t="s">
+      <c r="C51" s="45"/>
+      <c r="D51" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+    </row>
+    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="C52" s="68"/>
+      <c r="D52" s="69" t="s">
         <v>289</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-    </row>
-    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="C52" s="67"/>
-      <c r="D52" s="68" t="s">
+      <c r="E52" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>291</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -9822,15 +9902,15 @@
       <c r="M52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="C53" s="67"/>
-      <c r="D53" s="68" t="s">
+      <c r="B53" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="C53" s="68"/>
+      <c r="D53" s="69" t="s">
+        <v>291</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>292</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>293</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -9842,15 +9922,15 @@
       <c r="M53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="C54" s="67"/>
-      <c r="D54" s="68" t="s">
+      <c r="B54" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" s="68"/>
+      <c r="D54" s="69" t="s">
+        <v>293</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>294</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>295</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
@@ -9862,12 +9942,12 @@
       <c r="M54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="67" t="s">
-        <v>187</v>
-      </c>
-      <c r="C55" s="67"/>
-      <c r="D55" s="68" t="s">
-        <v>257</v>
+      <c r="B55" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="68"/>
+      <c r="D55" s="69" t="s">
+        <v>295</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>296</v>
@@ -9881,8 +9961,28 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
     </row>
+    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" s="68"/>
+      <c r="D56" s="69" t="s">
+        <v>258</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="110">
+  <mergeCells count="114">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:C4"/>
@@ -9972,17 +10072,19 @@
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="K43:M43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="K44:M44"/>
     <mergeCell ref="B45:G45"/>
     <mergeCell ref="H45:M45"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="H46:M46"/>
     <mergeCell ref="B47:G47"/>
     <mergeCell ref="H47:M47"/>
-    <mergeCell ref="B49:M49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="E50:M50"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="B50:M50"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="E51:M51"/>
     <mergeCell ref="B52:C52"/>
@@ -9993,8 +10095,10 @@
     <mergeCell ref="E54:M54"/>
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="E55:M55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="E56:M56"/>
   </mergeCells>
-  <conditionalFormatting sqref="E43:M43">
+  <conditionalFormatting sqref="E44:M44">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>

--- a/SWOT/SWOT-modelo.xlsx
+++ b/SWOT/SWOT-modelo.xlsx
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">W2 × O2</t>
   </si>
   <si>
-    <t xml:space="preserve">Implantar uma plataforma de cotação eletrônica no lugar das planilhas.</t>
+    <t xml:space="preserve">Implantar uma plataforma de cotação eletrônica no lugar das cotações por e-mail.</t>
   </si>
   <si>
     <t xml:space="preserve">Desenvolver fabricantes nacionais, com o apoio técnico dos compradores.</t>
@@ -1967,11 +1967,11 @@
         </c:ser>
         <c:gapWidth val="120"/>
         <c:overlap val="0"/>
-        <c:axId val="44875571"/>
-        <c:axId val="72586805"/>
+        <c:axId val="98210670"/>
+        <c:axId val="21385818"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="44875571"/>
+        <c:axId val="98210670"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2003,7 +2003,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72586805"/>
+        <c:crossAx val="21385818"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2011,7 +2011,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72586805"/>
+        <c:axId val="21385818"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2051,7 +2051,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44875571"/>
+        <c:crossAx val="98210670"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7071,12 +7071,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F6:F20" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="H6:H20" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F6:F20" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
